--- a/wwwroot/ExcelModel/Next_WET_sheet.xlsx
+++ b/wwwroot/ExcelModel/Next_WET_sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\NX-lims Softlines Command System\wwwroot\ExcelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF095EB-58AD-4CB4-8096-9F6CBA955776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50D5D6F-8FE1-4ABD-B9BA-953F93110DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8004" yWindow="456" windowWidth="15168" windowHeight="11364" tabRatio="768" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="768" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TM1-TM2-TM3" sheetId="36" r:id="rId1"/>
@@ -2975,6 +2975,9 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3092,9 +3095,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3151,6 +3151,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -3421,9 +3424,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4653,9 +4653,9 @@
       <c r="A2" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="AF2" s="275"/>
-      <c r="AG2" s="275"/>
-      <c r="AH2" s="275"/>
+      <c r="AF2" s="276"/>
+      <c r="AG2" s="276"/>
+      <c r="AH2" s="276"/>
       <c r="AI2" s="13" t="s">
         <v>343</v>
       </c>
@@ -4957,45 +4957,45 @@
       <c r="M9" s="186"/>
       <c r="N9" s="186"/>
       <c r="O9" s="186"/>
-      <c r="P9" s="267" t="s">
+      <c r="P9" s="268" t="s">
         <v>345</v>
       </c>
       <c r="Q9" s="186"/>
       <c r="R9" s="186"/>
       <c r="S9" s="186"/>
       <c r="T9" s="187"/>
-      <c r="U9" s="267" t="s">
+      <c r="U9" s="268" t="s">
         <v>293</v>
       </c>
-      <c r="V9" s="267"/>
+      <c r="V9" s="268"/>
       <c r="W9" s="92"/>
       <c r="X9" s="186" t="s">
         <v>31</v>
       </c>
       <c r="Y9" s="186"/>
-      <c r="Z9" s="268" t="s">
+      <c r="Z9" s="269" t="s">
         <v>293</v>
       </c>
-      <c r="AA9" s="267"/>
+      <c r="AA9" s="268"/>
       <c r="AB9" s="93"/>
       <c r="AC9" s="186" t="s">
         <v>31</v>
       </c>
       <c r="AD9" s="187"/>
-      <c r="AE9" s="268" t="s">
+      <c r="AE9" s="269" t="s">
         <v>294</v>
       </c>
-      <c r="AF9" s="267"/>
-      <c r="AG9" s="267"/>
-      <c r="AH9" s="267"/>
-      <c r="AI9" s="269"/>
-      <c r="AJ9" s="268" t="s">
+      <c r="AF9" s="268"/>
+      <c r="AG9" s="268"/>
+      <c r="AH9" s="268"/>
+      <c r="AI9" s="270"/>
+      <c r="AJ9" s="269" t="s">
         <v>294</v>
       </c>
-      <c r="AK9" s="267"/>
-      <c r="AL9" s="267"/>
-      <c r="AM9" s="267"/>
-      <c r="AN9" s="269"/>
+      <c r="AK9" s="268"/>
+      <c r="AL9" s="268"/>
+      <c r="AM9" s="268"/>
+      <c r="AN9" s="270"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="188"/>
@@ -5018,30 +5018,30 @@
       <c r="R10" s="189"/>
       <c r="S10" s="189"/>
       <c r="T10" s="190"/>
-      <c r="U10" s="270" t="s">
+      <c r="U10" s="271" t="s">
         <v>346</v>
       </c>
       <c r="V10" s="189"/>
       <c r="W10" s="189"/>
       <c r="X10" s="189"/>
       <c r="Y10" s="189"/>
-      <c r="Z10" s="264" t="s">
+      <c r="Z10" s="265" t="s">
         <v>346</v>
       </c>
       <c r="AA10" s="189"/>
       <c r="AB10" s="189"/>
       <c r="AC10" s="189"/>
       <c r="AD10" s="190"/>
-      <c r="AE10" s="264"/>
-      <c r="AF10" s="270"/>
-      <c r="AG10" s="270"/>
-      <c r="AH10" s="270"/>
-      <c r="AI10" s="271"/>
-      <c r="AJ10" s="264"/>
-      <c r="AK10" s="270"/>
-      <c r="AL10" s="270"/>
-      <c r="AM10" s="270"/>
-      <c r="AN10" s="271"/>
+      <c r="AE10" s="265"/>
+      <c r="AF10" s="271"/>
+      <c r="AG10" s="271"/>
+      <c r="AH10" s="271"/>
+      <c r="AI10" s="272"/>
+      <c r="AJ10" s="265"/>
+      <c r="AK10" s="271"/>
+      <c r="AL10" s="271"/>
+      <c r="AM10" s="271"/>
+      <c r="AN10" s="272"/>
     </row>
     <row r="11" spans="1:44" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="94" t="s">
@@ -5076,19 +5076,19 @@
       <c r="AB11" s="192"/>
       <c r="AC11" s="192"/>
       <c r="AD11" s="193"/>
-      <c r="AE11" s="265" t="s">
+      <c r="AE11" s="266" t="s">
         <v>293</v>
       </c>
-      <c r="AF11" s="266"/>
+      <c r="AF11" s="267"/>
       <c r="AG11" s="92"/>
       <c r="AH11" s="192" t="s">
         <v>31</v>
       </c>
       <c r="AI11" s="193"/>
-      <c r="AJ11" s="265" t="s">
+      <c r="AJ11" s="266" t="s">
         <v>293</v>
       </c>
-      <c r="AK11" s="266"/>
+      <c r="AK11" s="267"/>
       <c r="AL11" s="93"/>
       <c r="AM11" s="192" t="s">
         <v>31</v>
@@ -5697,31 +5697,31 @@
       <c r="J26" s="50"/>
       <c r="K26" s="50"/>
       <c r="L26" s="58"/>
-      <c r="P26" s="273"/>
-      <c r="Q26" s="274"/>
-      <c r="R26" s="274"/>
-      <c r="S26" s="274"/>
-      <c r="T26" s="274"/>
-      <c r="U26" s="274"/>
-      <c r="V26" s="274"/>
-      <c r="W26" s="274"/>
-      <c r="X26" s="274"/>
-      <c r="Y26" s="274"/>
-      <c r="Z26" s="274"/>
-      <c r="AA26" s="274"/>
-      <c r="AB26" s="274"/>
-      <c r="AC26" s="274"/>
-      <c r="AD26" s="274"/>
-      <c r="AE26" s="274"/>
-      <c r="AF26" s="274"/>
-      <c r="AG26" s="274"/>
-      <c r="AH26" s="274"/>
-      <c r="AI26" s="274"/>
-      <c r="AJ26" s="279"/>
-      <c r="AK26" s="280"/>
-      <c r="AL26" s="280"/>
-      <c r="AM26" s="280"/>
-      <c r="AN26" s="273"/>
+      <c r="P26" s="274"/>
+      <c r="Q26" s="275"/>
+      <c r="R26" s="275"/>
+      <c r="S26" s="275"/>
+      <c r="T26" s="275"/>
+      <c r="U26" s="275"/>
+      <c r="V26" s="275"/>
+      <c r="W26" s="275"/>
+      <c r="X26" s="275"/>
+      <c r="Y26" s="275"/>
+      <c r="Z26" s="275"/>
+      <c r="AA26" s="275"/>
+      <c r="AB26" s="275"/>
+      <c r="AC26" s="275"/>
+      <c r="AD26" s="275"/>
+      <c r="AE26" s="275"/>
+      <c r="AF26" s="275"/>
+      <c r="AG26" s="275"/>
+      <c r="AH26" s="275"/>
+      <c r="AI26" s="275"/>
+      <c r="AJ26" s="280"/>
+      <c r="AK26" s="281"/>
+      <c r="AL26" s="281"/>
+      <c r="AM26" s="281"/>
+      <c r="AN26" s="274"/>
     </row>
     <row r="27" spans="1:40" ht="18.600000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
@@ -5742,30 +5742,30 @@
       <c r="N27" s="96"/>
       <c r="O27" s="96"/>
       <c r="P27" s="193"/>
-      <c r="Q27" s="272"/>
-      <c r="R27" s="272"/>
-      <c r="S27" s="272"/>
-      <c r="T27" s="272"/>
-      <c r="U27" s="272"/>
-      <c r="V27" s="272"/>
-      <c r="W27" s="272"/>
-      <c r="X27" s="272"/>
-      <c r="Y27" s="272"/>
-      <c r="Z27" s="272"/>
-      <c r="AA27" s="272"/>
-      <c r="AB27" s="272"/>
-      <c r="AC27" s="272"/>
-      <c r="AD27" s="272"/>
-      <c r="AE27" s="272"/>
-      <c r="AF27" s="272"/>
-      <c r="AG27" s="272"/>
-      <c r="AH27" s="272"/>
-      <c r="AI27" s="272"/>
-      <c r="AJ27" s="276"/>
-      <c r="AK27" s="277"/>
-      <c r="AL27" s="277"/>
-      <c r="AM27" s="277"/>
-      <c r="AN27" s="278"/>
+      <c r="Q27" s="273"/>
+      <c r="R27" s="273"/>
+      <c r="S27" s="273"/>
+      <c r="T27" s="273"/>
+      <c r="U27" s="273"/>
+      <c r="V27" s="273"/>
+      <c r="W27" s="273"/>
+      <c r="X27" s="273"/>
+      <c r="Y27" s="273"/>
+      <c r="Z27" s="273"/>
+      <c r="AA27" s="273"/>
+      <c r="AB27" s="273"/>
+      <c r="AC27" s="273"/>
+      <c r="AD27" s="273"/>
+      <c r="AE27" s="273"/>
+      <c r="AF27" s="273"/>
+      <c r="AG27" s="273"/>
+      <c r="AH27" s="273"/>
+      <c r="AI27" s="273"/>
+      <c r="AJ27" s="277"/>
+      <c r="AK27" s="278"/>
+      <c r="AL27" s="278"/>
+      <c r="AM27" s="278"/>
+      <c r="AN27" s="279"/>
     </row>
     <row r="28" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
@@ -6176,32 +6176,32 @@
       <c r="T42" s="173"/>
       <c r="U42" s="173"/>
       <c r="V42" s="173"/>
-      <c r="W42" s="262" t="s">
+      <c r="W42" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="X42" s="263"/>
-      <c r="Y42" s="263"/>
-      <c r="Z42" s="350"/>
-      <c r="AA42" s="350"/>
-      <c r="AB42" s="260" t="s">
+      <c r="X42" s="264"/>
+      <c r="Y42" s="264"/>
+      <c r="Z42" s="260"/>
+      <c r="AA42" s="260"/>
+      <c r="AB42" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="AC42" s="260"/>
-      <c r="AD42" s="260"/>
-      <c r="AE42" s="261"/>
-      <c r="AF42" s="262" t="s">
+      <c r="AC42" s="261"/>
+      <c r="AD42" s="261"/>
+      <c r="AE42" s="262"/>
+      <c r="AF42" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="AG42" s="263"/>
-      <c r="AH42" s="263"/>
-      <c r="AI42" s="350"/>
-      <c r="AJ42" s="350"/>
-      <c r="AK42" s="260" t="s">
+      <c r="AG42" s="264"/>
+      <c r="AH42" s="264"/>
+      <c r="AI42" s="260"/>
+      <c r="AJ42" s="260"/>
+      <c r="AK42" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="AL42" s="260"/>
-      <c r="AM42" s="260"/>
-      <c r="AN42" s="261"/>
+      <c r="AL42" s="261"/>
+      <c r="AM42" s="261"/>
+      <c r="AN42" s="262"/>
     </row>
     <row r="43" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A43" s="191"/>
@@ -6614,33 +6614,33 @@
       <c r="A1" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="281"/>
-      <c r="O1" s="281"/>
-      <c r="P1" s="281"/>
-      <c r="Q1" s="281"/>
-      <c r="R1" s="281"/>
-      <c r="S1" s="281"/>
-      <c r="T1" s="281"/>
-      <c r="U1" s="281"/>
-      <c r="V1" s="281"/>
-      <c r="W1" s="281"/>
-      <c r="X1" s="281"/>
-      <c r="Y1" s="281"/>
-      <c r="Z1" s="281"/>
-      <c r="AA1" s="281"/>
-      <c r="AB1" s="281"/>
-      <c r="AC1" s="281"/>
-      <c r="AD1" s="281"/>
-      <c r="AE1" s="281"/>
-      <c r="AF1" s="281"/>
-      <c r="AG1" s="281"/>
-      <c r="AH1" s="281"/>
-      <c r="AI1" s="281"/>
-      <c r="AJ1" s="281"/>
-      <c r="AK1" s="281"/>
-      <c r="AL1" s="281"/>
-      <c r="AM1" s="281"/>
-      <c r="AN1" s="281"/>
+      <c r="N1" s="282"/>
+      <c r="O1" s="282"/>
+      <c r="P1" s="282"/>
+      <c r="Q1" s="282"/>
+      <c r="R1" s="282"/>
+      <c r="S1" s="282"/>
+      <c r="T1" s="282"/>
+      <c r="U1" s="282"/>
+      <c r="V1" s="282"/>
+      <c r="W1" s="282"/>
+      <c r="X1" s="282"/>
+      <c r="Y1" s="282"/>
+      <c r="Z1" s="282"/>
+      <c r="AA1" s="282"/>
+      <c r="AB1" s="282"/>
+      <c r="AC1" s="282"/>
+      <c r="AD1" s="282"/>
+      <c r="AE1" s="282"/>
+      <c r="AF1" s="282"/>
+      <c r="AG1" s="282"/>
+      <c r="AH1" s="282"/>
+      <c r="AI1" s="282"/>
+      <c r="AJ1" s="282"/>
+      <c r="AK1" s="282"/>
+      <c r="AL1" s="282"/>
+      <c r="AM1" s="282"/>
+      <c r="AN1" s="282"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -6675,9 +6675,9 @@
       <c r="AB2" s="12"/>
       <c r="AC2" s="12"/>
       <c r="AD2" s="12"/>
-      <c r="AE2" s="226"/>
-      <c r="AF2" s="226"/>
-      <c r="AG2" s="226"/>
+      <c r="AE2" s="227"/>
+      <c r="AF2" s="227"/>
+      <c r="AG2" s="227"/>
       <c r="AH2" s="13" t="s">
         <v>287</v>
       </c>
@@ -6970,110 +6970,110 @@
       <c r="AN8" s="112"/>
     </row>
     <row r="9" spans="1:43" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="288" t="s">
+      <c r="A9" s="289" t="s">
         <v>319</v>
       </c>
-      <c r="B9" s="289"/>
-      <c r="C9" s="289"/>
-      <c r="D9" s="289"/>
-      <c r="E9" s="289"/>
-      <c r="F9" s="289"/>
-      <c r="G9" s="289"/>
-      <c r="H9" s="289"/>
-      <c r="I9" s="289"/>
-      <c r="J9" s="289"/>
-      <c r="K9" s="289"/>
+      <c r="B9" s="290"/>
+      <c r="C9" s="290"/>
+      <c r="D9" s="290"/>
+      <c r="E9" s="290"/>
+      <c r="F9" s="290"/>
+      <c r="G9" s="290"/>
+      <c r="H9" s="290"/>
+      <c r="I9" s="290"/>
+      <c r="J9" s="290"/>
+      <c r="K9" s="290"/>
       <c r="L9" s="103"/>
       <c r="M9" s="103"/>
       <c r="N9" s="103"/>
       <c r="O9" s="103"/>
-      <c r="P9" s="292" t="s">
+      <c r="P9" s="293" t="s">
         <v>345</v>
       </c>
-      <c r="Q9" s="293"/>
-      <c r="R9" s="293"/>
-      <c r="S9" s="293"/>
-      <c r="T9" s="294"/>
-      <c r="U9" s="295" t="s">
+      <c r="Q9" s="294"/>
+      <c r="R9" s="294"/>
+      <c r="S9" s="294"/>
+      <c r="T9" s="295"/>
+      <c r="U9" s="296" t="s">
         <v>293</v>
       </c>
-      <c r="V9" s="295"/>
+      <c r="V9" s="296"/>
       <c r="W9" s="104"/>
-      <c r="X9" s="293" t="s">
+      <c r="X9" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="Y9" s="293"/>
-      <c r="Z9" s="296" t="s">
+      <c r="Y9" s="294"/>
+      <c r="Z9" s="297" t="s">
         <v>293</v>
       </c>
-      <c r="AA9" s="295"/>
+      <c r="AA9" s="296"/>
       <c r="AB9" s="104"/>
-      <c r="AC9" s="293" t="s">
+      <c r="AC9" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="AD9" s="294"/>
-      <c r="AE9" s="296" t="s">
+      <c r="AD9" s="295"/>
+      <c r="AE9" s="297" t="s">
         <v>294</v>
       </c>
-      <c r="AF9" s="295"/>
-      <c r="AG9" s="295"/>
-      <c r="AH9" s="295"/>
-      <c r="AI9" s="297"/>
-      <c r="AJ9" s="296" t="s">
+      <c r="AF9" s="296"/>
+      <c r="AG9" s="296"/>
+      <c r="AH9" s="296"/>
+      <c r="AI9" s="298"/>
+      <c r="AJ9" s="297" t="s">
         <v>294</v>
       </c>
-      <c r="AK9" s="295"/>
-      <c r="AL9" s="295"/>
-      <c r="AM9" s="295"/>
-      <c r="AN9" s="297"/>
+      <c r="AK9" s="296"/>
+      <c r="AL9" s="296"/>
+      <c r="AM9" s="296"/>
+      <c r="AN9" s="298"/>
       <c r="AO9" s="101"/>
       <c r="AP9" s="101"/>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A10" s="290"/>
-      <c r="B10" s="291"/>
-      <c r="C10" s="291"/>
-      <c r="D10" s="291"/>
-      <c r="E10" s="291"/>
-      <c r="F10" s="291"/>
-      <c r="G10" s="291"/>
-      <c r="H10" s="291"/>
-      <c r="I10" s="291"/>
-      <c r="J10" s="291"/>
-      <c r="K10" s="291"/>
+      <c r="A10" s="291"/>
+      <c r="B10" s="292"/>
+      <c r="C10" s="292"/>
+      <c r="D10" s="292"/>
+      <c r="E10" s="292"/>
+      <c r="F10" s="292"/>
+      <c r="G10" s="292"/>
+      <c r="H10" s="292"/>
+      <c r="I10" s="292"/>
+      <c r="J10" s="292"/>
+      <c r="K10" s="292"/>
       <c r="L10" s="101"/>
       <c r="M10" s="101"/>
       <c r="N10" s="101"/>
       <c r="O10" s="101"/>
-      <c r="P10" s="283"/>
-      <c r="Q10" s="283"/>
-      <c r="R10" s="283"/>
-      <c r="S10" s="283"/>
-      <c r="T10" s="284"/>
-      <c r="U10" s="301" t="s">
+      <c r="P10" s="284"/>
+      <c r="Q10" s="284"/>
+      <c r="R10" s="284"/>
+      <c r="S10" s="284"/>
+      <c r="T10" s="285"/>
+      <c r="U10" s="302" t="s">
         <v>346</v>
       </c>
-      <c r="V10" s="283"/>
-      <c r="W10" s="283"/>
-      <c r="X10" s="283"/>
-      <c r="Y10" s="283"/>
-      <c r="Z10" s="282" t="s">
+      <c r="V10" s="284"/>
+      <c r="W10" s="284"/>
+      <c r="X10" s="284"/>
+      <c r="Y10" s="284"/>
+      <c r="Z10" s="283" t="s">
         <v>346</v>
       </c>
-      <c r="AA10" s="283"/>
-      <c r="AB10" s="283"/>
-      <c r="AC10" s="283"/>
-      <c r="AD10" s="284"/>
-      <c r="AE10" s="298"/>
-      <c r="AF10" s="299"/>
-      <c r="AG10" s="299"/>
-      <c r="AH10" s="299"/>
-      <c r="AI10" s="300"/>
-      <c r="AJ10" s="298"/>
-      <c r="AK10" s="299"/>
-      <c r="AL10" s="299"/>
-      <c r="AM10" s="299"/>
-      <c r="AN10" s="300"/>
+      <c r="AA10" s="284"/>
+      <c r="AB10" s="284"/>
+      <c r="AC10" s="284"/>
+      <c r="AD10" s="285"/>
+      <c r="AE10" s="299"/>
+      <c r="AF10" s="300"/>
+      <c r="AG10" s="300"/>
+      <c r="AH10" s="300"/>
+      <c r="AI10" s="301"/>
+      <c r="AJ10" s="299"/>
+      <c r="AK10" s="300"/>
+      <c r="AL10" s="300"/>
+      <c r="AM10" s="300"/>
+      <c r="AN10" s="301"/>
       <c r="AO10" s="101"/>
       <c r="AP10" s="101"/>
     </row>
@@ -7085,49 +7085,49 @@
       <c r="C11" s="106"/>
       <c r="D11" s="106"/>
       <c r="E11" s="106"/>
-      <c r="F11" s="281"/>
-      <c r="G11" s="281"/>
-      <c r="H11" s="281"/>
-      <c r="I11" s="281"/>
-      <c r="J11" s="281"/>
-      <c r="K11" s="281"/>
-      <c r="L11" s="281"/>
-      <c r="M11" s="281"/>
-      <c r="N11" s="281"/>
-      <c r="O11" s="281"/>
-      <c r="P11" s="286"/>
-      <c r="Q11" s="286"/>
-      <c r="R11" s="286"/>
-      <c r="S11" s="286"/>
-      <c r="T11" s="287"/>
-      <c r="U11" s="286"/>
-      <c r="V11" s="286"/>
-      <c r="W11" s="286"/>
-      <c r="X11" s="286"/>
-      <c r="Y11" s="286"/>
-      <c r="Z11" s="285"/>
-      <c r="AA11" s="286"/>
-      <c r="AB11" s="286"/>
-      <c r="AC11" s="286"/>
-      <c r="AD11" s="287"/>
-      <c r="AE11" s="285" t="s">
+      <c r="F11" s="282"/>
+      <c r="G11" s="282"/>
+      <c r="H11" s="282"/>
+      <c r="I11" s="282"/>
+      <c r="J11" s="282"/>
+      <c r="K11" s="282"/>
+      <c r="L11" s="282"/>
+      <c r="M11" s="282"/>
+      <c r="N11" s="282"/>
+      <c r="O11" s="282"/>
+      <c r="P11" s="287"/>
+      <c r="Q11" s="287"/>
+      <c r="R11" s="287"/>
+      <c r="S11" s="287"/>
+      <c r="T11" s="288"/>
+      <c r="U11" s="287"/>
+      <c r="V11" s="287"/>
+      <c r="W11" s="287"/>
+      <c r="X11" s="287"/>
+      <c r="Y11" s="287"/>
+      <c r="Z11" s="286"/>
+      <c r="AA11" s="287"/>
+      <c r="AB11" s="287"/>
+      <c r="AC11" s="287"/>
+      <c r="AD11" s="288"/>
+      <c r="AE11" s="286" t="s">
         <v>293</v>
       </c>
-      <c r="AF11" s="286"/>
+      <c r="AF11" s="287"/>
       <c r="AG11" s="107"/>
-      <c r="AH11" s="286" t="s">
+      <c r="AH11" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="AI11" s="287"/>
-      <c r="AJ11" s="285" t="s">
+      <c r="AI11" s="288"/>
+      <c r="AJ11" s="286" t="s">
         <v>293</v>
       </c>
-      <c r="AK11" s="286"/>
+      <c r="AK11" s="287"/>
       <c r="AL11" s="107"/>
-      <c r="AM11" s="286" t="s">
+      <c r="AM11" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="AN11" s="287"/>
+      <c r="AN11" s="288"/>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="108" t="s">
@@ -7142,36 +7142,36 @@
       <c r="H12" s="110"/>
       <c r="I12" s="110"/>
       <c r="J12" s="110"/>
-      <c r="K12" s="304"/>
-      <c r="L12" s="304"/>
-      <c r="M12" s="304"/>
-      <c r="N12" s="304"/>
-      <c r="O12" s="304"/>
-      <c r="P12" s="303"/>
-      <c r="Q12" s="302"/>
-      <c r="R12" s="302"/>
-      <c r="S12" s="302"/>
-      <c r="T12" s="302"/>
-      <c r="U12" s="302"/>
-      <c r="V12" s="302"/>
-      <c r="W12" s="302"/>
-      <c r="X12" s="302"/>
-      <c r="Y12" s="302"/>
-      <c r="Z12" s="302"/>
-      <c r="AA12" s="302"/>
-      <c r="AB12" s="302"/>
-      <c r="AC12" s="302"/>
-      <c r="AD12" s="302"/>
-      <c r="AE12" s="302"/>
-      <c r="AF12" s="302"/>
-      <c r="AG12" s="302"/>
-      <c r="AH12" s="302"/>
-      <c r="AI12" s="302"/>
-      <c r="AJ12" s="302"/>
-      <c r="AK12" s="302"/>
-      <c r="AL12" s="302"/>
-      <c r="AM12" s="302"/>
-      <c r="AN12" s="302"/>
+      <c r="K12" s="305"/>
+      <c r="L12" s="305"/>
+      <c r="M12" s="305"/>
+      <c r="N12" s="305"/>
+      <c r="O12" s="305"/>
+      <c r="P12" s="304"/>
+      <c r="Q12" s="303"/>
+      <c r="R12" s="303"/>
+      <c r="S12" s="303"/>
+      <c r="T12" s="303"/>
+      <c r="U12" s="303"/>
+      <c r="V12" s="303"/>
+      <c r="W12" s="303"/>
+      <c r="X12" s="303"/>
+      <c r="Y12" s="303"/>
+      <c r="Z12" s="303"/>
+      <c r="AA12" s="303"/>
+      <c r="AB12" s="303"/>
+      <c r="AC12" s="303"/>
+      <c r="AD12" s="303"/>
+      <c r="AE12" s="303"/>
+      <c r="AF12" s="303"/>
+      <c r="AG12" s="303"/>
+      <c r="AH12" s="303"/>
+      <c r="AI12" s="303"/>
+      <c r="AJ12" s="303"/>
+      <c r="AK12" s="303"/>
+      <c r="AL12" s="303"/>
+      <c r="AM12" s="303"/>
+      <c r="AN12" s="303"/>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="111" t="s">
@@ -7181,36 +7181,36 @@
       <c r="H13" s="112"/>
       <c r="I13" s="112"/>
       <c r="J13" s="112"/>
-      <c r="K13" s="305"/>
-      <c r="L13" s="305"/>
-      <c r="M13" s="305"/>
-      <c r="N13" s="305"/>
-      <c r="O13" s="305"/>
-      <c r="P13" s="303"/>
-      <c r="Q13" s="302"/>
-      <c r="R13" s="302"/>
-      <c r="S13" s="302"/>
-      <c r="T13" s="302"/>
-      <c r="U13" s="302"/>
-      <c r="V13" s="302"/>
-      <c r="W13" s="302"/>
-      <c r="X13" s="302"/>
-      <c r="Y13" s="302"/>
-      <c r="Z13" s="302"/>
-      <c r="AA13" s="302"/>
-      <c r="AB13" s="302"/>
-      <c r="AC13" s="302"/>
-      <c r="AD13" s="302"/>
-      <c r="AE13" s="302"/>
-      <c r="AF13" s="302"/>
-      <c r="AG13" s="302"/>
-      <c r="AH13" s="302"/>
-      <c r="AI13" s="302"/>
-      <c r="AJ13" s="302"/>
-      <c r="AK13" s="302"/>
-      <c r="AL13" s="302"/>
-      <c r="AM13" s="302"/>
-      <c r="AN13" s="302"/>
+      <c r="K13" s="306"/>
+      <c r="L13" s="306"/>
+      <c r="M13" s="306"/>
+      <c r="N13" s="306"/>
+      <c r="O13" s="306"/>
+      <c r="P13" s="304"/>
+      <c r="Q13" s="303"/>
+      <c r="R13" s="303"/>
+      <c r="S13" s="303"/>
+      <c r="T13" s="303"/>
+      <c r="U13" s="303"/>
+      <c r="V13" s="303"/>
+      <c r="W13" s="303"/>
+      <c r="X13" s="303"/>
+      <c r="Y13" s="303"/>
+      <c r="Z13" s="303"/>
+      <c r="AA13" s="303"/>
+      <c r="AB13" s="303"/>
+      <c r="AC13" s="303"/>
+      <c r="AD13" s="303"/>
+      <c r="AE13" s="303"/>
+      <c r="AF13" s="303"/>
+      <c r="AG13" s="303"/>
+      <c r="AH13" s="303"/>
+      <c r="AI13" s="303"/>
+      <c r="AJ13" s="303"/>
+      <c r="AK13" s="303"/>
+      <c r="AL13" s="303"/>
+      <c r="AM13" s="303"/>
+      <c r="AN13" s="303"/>
     </row>
     <row r="14" spans="1:43" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="111" t="s">
@@ -7220,36 +7220,36 @@
       <c r="H14" s="112"/>
       <c r="I14" s="112"/>
       <c r="J14" s="112"/>
-      <c r="K14" s="305"/>
-      <c r="L14" s="305"/>
-      <c r="M14" s="305"/>
-      <c r="N14" s="305"/>
-      <c r="O14" s="305"/>
-      <c r="P14" s="303"/>
-      <c r="Q14" s="302"/>
-      <c r="R14" s="302"/>
-      <c r="S14" s="302"/>
-      <c r="T14" s="302"/>
-      <c r="U14" s="302"/>
-      <c r="V14" s="302"/>
-      <c r="W14" s="302"/>
-      <c r="X14" s="302"/>
-      <c r="Y14" s="302"/>
-      <c r="Z14" s="302"/>
-      <c r="AA14" s="302"/>
-      <c r="AB14" s="302"/>
-      <c r="AC14" s="302"/>
-      <c r="AD14" s="302"/>
-      <c r="AE14" s="302"/>
-      <c r="AF14" s="302"/>
-      <c r="AG14" s="302"/>
-      <c r="AH14" s="302"/>
-      <c r="AI14" s="302"/>
-      <c r="AJ14" s="302"/>
-      <c r="AK14" s="302"/>
-      <c r="AL14" s="302"/>
-      <c r="AM14" s="302"/>
-      <c r="AN14" s="302"/>
+      <c r="K14" s="306"/>
+      <c r="L14" s="306"/>
+      <c r="M14" s="306"/>
+      <c r="N14" s="306"/>
+      <c r="O14" s="306"/>
+      <c r="P14" s="304"/>
+      <c r="Q14" s="303"/>
+      <c r="R14" s="303"/>
+      <c r="S14" s="303"/>
+      <c r="T14" s="303"/>
+      <c r="U14" s="303"/>
+      <c r="V14" s="303"/>
+      <c r="W14" s="303"/>
+      <c r="X14" s="303"/>
+      <c r="Y14" s="303"/>
+      <c r="Z14" s="303"/>
+      <c r="AA14" s="303"/>
+      <c r="AB14" s="303"/>
+      <c r="AC14" s="303"/>
+      <c r="AD14" s="303"/>
+      <c r="AE14" s="303"/>
+      <c r="AF14" s="303"/>
+      <c r="AG14" s="303"/>
+      <c r="AH14" s="303"/>
+      <c r="AI14" s="303"/>
+      <c r="AJ14" s="303"/>
+      <c r="AK14" s="303"/>
+      <c r="AL14" s="303"/>
+      <c r="AM14" s="303"/>
+      <c r="AN14" s="303"/>
     </row>
     <row r="15" spans="1:43" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="111" t="s">
@@ -7259,36 +7259,36 @@
       <c r="H15" s="112"/>
       <c r="I15" s="112"/>
       <c r="J15" s="112"/>
-      <c r="K15" s="305"/>
-      <c r="L15" s="305"/>
-      <c r="M15" s="305"/>
-      <c r="N15" s="305"/>
-      <c r="O15" s="305"/>
-      <c r="P15" s="303"/>
-      <c r="Q15" s="302"/>
-      <c r="R15" s="302"/>
-      <c r="S15" s="302"/>
-      <c r="T15" s="302"/>
-      <c r="U15" s="302"/>
-      <c r="V15" s="302"/>
-      <c r="W15" s="302"/>
-      <c r="X15" s="302"/>
-      <c r="Y15" s="302"/>
-      <c r="Z15" s="302"/>
-      <c r="AA15" s="302"/>
-      <c r="AB15" s="302"/>
-      <c r="AC15" s="302"/>
-      <c r="AD15" s="302"/>
-      <c r="AE15" s="302"/>
-      <c r="AF15" s="302"/>
-      <c r="AG15" s="302"/>
-      <c r="AH15" s="302"/>
-      <c r="AI15" s="302"/>
-      <c r="AJ15" s="302"/>
-      <c r="AK15" s="302"/>
-      <c r="AL15" s="302"/>
-      <c r="AM15" s="302"/>
-      <c r="AN15" s="302"/>
+      <c r="K15" s="306"/>
+      <c r="L15" s="306"/>
+      <c r="M15" s="306"/>
+      <c r="N15" s="306"/>
+      <c r="O15" s="306"/>
+      <c r="P15" s="304"/>
+      <c r="Q15" s="303"/>
+      <c r="R15" s="303"/>
+      <c r="S15" s="303"/>
+      <c r="T15" s="303"/>
+      <c r="U15" s="303"/>
+      <c r="V15" s="303"/>
+      <c r="W15" s="303"/>
+      <c r="X15" s="303"/>
+      <c r="Y15" s="303"/>
+      <c r="Z15" s="303"/>
+      <c r="AA15" s="303"/>
+      <c r="AB15" s="303"/>
+      <c r="AC15" s="303"/>
+      <c r="AD15" s="303"/>
+      <c r="AE15" s="303"/>
+      <c r="AF15" s="303"/>
+      <c r="AG15" s="303"/>
+      <c r="AH15" s="303"/>
+      <c r="AI15" s="303"/>
+      <c r="AJ15" s="303"/>
+      <c r="AK15" s="303"/>
+      <c r="AL15" s="303"/>
+      <c r="AM15" s="303"/>
+      <c r="AN15" s="303"/>
     </row>
     <row r="16" spans="1:43" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="113" t="s">
@@ -7303,182 +7303,182 @@
       <c r="H16" s="100"/>
       <c r="I16" s="100"/>
       <c r="J16" s="100"/>
-      <c r="K16" s="281"/>
-      <c r="L16" s="281"/>
-      <c r="M16" s="281"/>
-      <c r="N16" s="281"/>
-      <c r="O16" s="281"/>
-      <c r="P16" s="303"/>
-      <c r="Q16" s="302"/>
-      <c r="R16" s="302"/>
-      <c r="S16" s="302"/>
-      <c r="T16" s="302"/>
-      <c r="U16" s="302"/>
-      <c r="V16" s="302"/>
-      <c r="W16" s="302"/>
-      <c r="X16" s="302"/>
-      <c r="Y16" s="302"/>
-      <c r="Z16" s="302"/>
-      <c r="AA16" s="302"/>
-      <c r="AB16" s="302"/>
-      <c r="AC16" s="302"/>
-      <c r="AD16" s="302"/>
-      <c r="AE16" s="302"/>
-      <c r="AF16" s="302"/>
-      <c r="AG16" s="302"/>
-      <c r="AH16" s="302"/>
-      <c r="AI16" s="302"/>
-      <c r="AJ16" s="302"/>
-      <c r="AK16" s="302"/>
-      <c r="AL16" s="302"/>
-      <c r="AM16" s="302"/>
-      <c r="AN16" s="302"/>
+      <c r="K16" s="282"/>
+      <c r="L16" s="282"/>
+      <c r="M16" s="282"/>
+      <c r="N16" s="282"/>
+      <c r="O16" s="282"/>
+      <c r="P16" s="304"/>
+      <c r="Q16" s="303"/>
+      <c r="R16" s="303"/>
+      <c r="S16" s="303"/>
+      <c r="T16" s="303"/>
+      <c r="U16" s="303"/>
+      <c r="V16" s="303"/>
+      <c r="W16" s="303"/>
+      <c r="X16" s="303"/>
+      <c r="Y16" s="303"/>
+      <c r="Z16" s="303"/>
+      <c r="AA16" s="303"/>
+      <c r="AB16" s="303"/>
+      <c r="AC16" s="303"/>
+      <c r="AD16" s="303"/>
+      <c r="AE16" s="303"/>
+      <c r="AF16" s="303"/>
+      <c r="AG16" s="303"/>
+      <c r="AH16" s="303"/>
+      <c r="AI16" s="303"/>
+      <c r="AJ16" s="303"/>
+      <c r="AK16" s="303"/>
+      <c r="AL16" s="303"/>
+      <c r="AM16" s="303"/>
+      <c r="AN16" s="303"/>
     </row>
     <row r="17" spans="1:40" ht="7.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="306"/>
-      <c r="B17" s="306"/>
-      <c r="C17" s="306"/>
-      <c r="D17" s="306"/>
-      <c r="E17" s="306"/>
-      <c r="F17" s="306"/>
-      <c r="G17" s="306"/>
-      <c r="H17" s="306"/>
-      <c r="I17" s="306"/>
-      <c r="J17" s="306"/>
-      <c r="K17" s="306"/>
-      <c r="L17" s="306"/>
-      <c r="M17" s="306"/>
-      <c r="N17" s="306"/>
-      <c r="O17" s="306"/>
-      <c r="P17" s="306"/>
-      <c r="Q17" s="306"/>
-      <c r="R17" s="306"/>
-      <c r="S17" s="306"/>
-      <c r="T17" s="306"/>
-      <c r="U17" s="306"/>
-      <c r="V17" s="306"/>
-      <c r="W17" s="306"/>
-      <c r="X17" s="306"/>
-      <c r="Y17" s="306"/>
-      <c r="Z17" s="306"/>
-      <c r="AA17" s="306"/>
-      <c r="AB17" s="306"/>
-      <c r="AC17" s="306"/>
-      <c r="AD17" s="306"/>
-      <c r="AE17" s="306"/>
-      <c r="AF17" s="306"/>
-      <c r="AG17" s="306"/>
-      <c r="AH17" s="306"/>
-      <c r="AI17" s="306"/>
-      <c r="AJ17" s="306"/>
-      <c r="AK17" s="306"/>
-      <c r="AL17" s="306"/>
-      <c r="AM17" s="306"/>
-      <c r="AN17" s="306"/>
+      <c r="A17" s="307"/>
+      <c r="B17" s="307"/>
+      <c r="C17" s="307"/>
+      <c r="D17" s="307"/>
+      <c r="E17" s="307"/>
+      <c r="F17" s="307"/>
+      <c r="G17" s="307"/>
+      <c r="H17" s="307"/>
+      <c r="I17" s="307"/>
+      <c r="J17" s="307"/>
+      <c r="K17" s="307"/>
+      <c r="L17" s="307"/>
+      <c r="M17" s="307"/>
+      <c r="N17" s="307"/>
+      <c r="O17" s="307"/>
+      <c r="P17" s="307"/>
+      <c r="Q17" s="307"/>
+      <c r="R17" s="307"/>
+      <c r="S17" s="307"/>
+      <c r="T17" s="307"/>
+      <c r="U17" s="307"/>
+      <c r="V17" s="307"/>
+      <c r="W17" s="307"/>
+      <c r="X17" s="307"/>
+      <c r="Y17" s="307"/>
+      <c r="Z17" s="307"/>
+      <c r="AA17" s="307"/>
+      <c r="AB17" s="307"/>
+      <c r="AC17" s="307"/>
+      <c r="AD17" s="307"/>
+      <c r="AE17" s="307"/>
+      <c r="AF17" s="307"/>
+      <c r="AG17" s="307"/>
+      <c r="AH17" s="307"/>
+      <c r="AI17" s="307"/>
+      <c r="AJ17" s="307"/>
+      <c r="AK17" s="307"/>
+      <c r="AL17" s="307"/>
+      <c r="AM17" s="307"/>
+      <c r="AN17" s="307"/>
     </row>
     <row r="18" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="288" t="s">
+      <c r="A18" s="289" t="s">
         <v>325</v>
       </c>
-      <c r="B18" s="289"/>
-      <c r="C18" s="289"/>
-      <c r="D18" s="289"/>
-      <c r="E18" s="289"/>
-      <c r="F18" s="289"/>
-      <c r="G18" s="289"/>
-      <c r="H18" s="289"/>
-      <c r="I18" s="289"/>
-      <c r="J18" s="289"/>
-      <c r="K18" s="289"/>
+      <c r="B18" s="290"/>
+      <c r="C18" s="290"/>
+      <c r="D18" s="290"/>
+      <c r="E18" s="290"/>
+      <c r="F18" s="290"/>
+      <c r="G18" s="290"/>
+      <c r="H18" s="290"/>
+      <c r="I18" s="290"/>
+      <c r="J18" s="290"/>
+      <c r="K18" s="290"/>
       <c r="L18" s="103"/>
       <c r="M18" s="103"/>
       <c r="N18" s="103"/>
       <c r="O18" s="103"/>
-      <c r="P18" s="292" t="s">
+      <c r="P18" s="293" t="s">
         <v>345</v>
       </c>
-      <c r="Q18" s="293"/>
-      <c r="R18" s="293"/>
-      <c r="S18" s="293"/>
-      <c r="T18" s="294"/>
-      <c r="U18" s="295" t="s">
+      <c r="Q18" s="294"/>
+      <c r="R18" s="294"/>
+      <c r="S18" s="294"/>
+      <c r="T18" s="295"/>
+      <c r="U18" s="296" t="s">
         <v>293</v>
       </c>
-      <c r="V18" s="295"/>
+      <c r="V18" s="296"/>
       <c r="W18" s="104"/>
-      <c r="X18" s="293" t="s">
+      <c r="X18" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="Y18" s="293"/>
-      <c r="Z18" s="296" t="s">
+      <c r="Y18" s="294"/>
+      <c r="Z18" s="297" t="s">
         <v>293</v>
       </c>
-      <c r="AA18" s="295"/>
+      <c r="AA18" s="296"/>
       <c r="AB18" s="104"/>
-      <c r="AC18" s="293" t="s">
+      <c r="AC18" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="AD18" s="294"/>
-      <c r="AE18" s="296" t="s">
+      <c r="AD18" s="295"/>
+      <c r="AE18" s="297" t="s">
         <v>294</v>
       </c>
-      <c r="AF18" s="295"/>
-      <c r="AG18" s="295"/>
-      <c r="AH18" s="295"/>
-      <c r="AI18" s="297"/>
-      <c r="AJ18" s="296" t="s">
+      <c r="AF18" s="296"/>
+      <c r="AG18" s="296"/>
+      <c r="AH18" s="296"/>
+      <c r="AI18" s="298"/>
+      <c r="AJ18" s="297" t="s">
         <v>294</v>
       </c>
-      <c r="AK18" s="295"/>
-      <c r="AL18" s="295"/>
-      <c r="AM18" s="295"/>
-      <c r="AN18" s="297"/>
+      <c r="AK18" s="296"/>
+      <c r="AL18" s="296"/>
+      <c r="AM18" s="296"/>
+      <c r="AN18" s="298"/>
     </row>
     <row r="19" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="290"/>
-      <c r="B19" s="291"/>
-      <c r="C19" s="291"/>
-      <c r="D19" s="291"/>
-      <c r="E19" s="291"/>
-      <c r="F19" s="291"/>
-      <c r="G19" s="291"/>
-      <c r="H19" s="291"/>
-      <c r="I19" s="291"/>
-      <c r="J19" s="291"/>
-      <c r="K19" s="291"/>
+      <c r="A19" s="291"/>
+      <c r="B19" s="292"/>
+      <c r="C19" s="292"/>
+      <c r="D19" s="292"/>
+      <c r="E19" s="292"/>
+      <c r="F19" s="292"/>
+      <c r="G19" s="292"/>
+      <c r="H19" s="292"/>
+      <c r="I19" s="292"/>
+      <c r="J19" s="292"/>
+      <c r="K19" s="292"/>
       <c r="L19" s="101"/>
       <c r="M19" s="101"/>
       <c r="N19" s="101"/>
       <c r="O19" s="101"/>
-      <c r="P19" s="283"/>
-      <c r="Q19" s="283"/>
-      <c r="R19" s="283"/>
-      <c r="S19" s="283"/>
-      <c r="T19" s="284"/>
-      <c r="U19" s="301" t="s">
+      <c r="P19" s="284"/>
+      <c r="Q19" s="284"/>
+      <c r="R19" s="284"/>
+      <c r="S19" s="284"/>
+      <c r="T19" s="285"/>
+      <c r="U19" s="302" t="s">
         <v>346</v>
       </c>
-      <c r="V19" s="283"/>
-      <c r="W19" s="283"/>
-      <c r="X19" s="283"/>
-      <c r="Y19" s="283"/>
-      <c r="Z19" s="301" t="s">
+      <c r="V19" s="284"/>
+      <c r="W19" s="284"/>
+      <c r="X19" s="284"/>
+      <c r="Y19" s="284"/>
+      <c r="Z19" s="302" t="s">
         <v>346</v>
       </c>
-      <c r="AA19" s="283"/>
-      <c r="AB19" s="283"/>
-      <c r="AC19" s="283"/>
-      <c r="AD19" s="283"/>
-      <c r="AE19" s="298"/>
-      <c r="AF19" s="299"/>
-      <c r="AG19" s="299"/>
-      <c r="AH19" s="299"/>
-      <c r="AI19" s="300"/>
-      <c r="AJ19" s="298"/>
-      <c r="AK19" s="299"/>
-      <c r="AL19" s="299"/>
-      <c r="AM19" s="299"/>
-      <c r="AN19" s="300"/>
+      <c r="AA19" s="284"/>
+      <c r="AB19" s="284"/>
+      <c r="AC19" s="284"/>
+      <c r="AD19" s="284"/>
+      <c r="AE19" s="299"/>
+      <c r="AF19" s="300"/>
+      <c r="AG19" s="300"/>
+      <c r="AH19" s="300"/>
+      <c r="AI19" s="301"/>
+      <c r="AJ19" s="299"/>
+      <c r="AK19" s="300"/>
+      <c r="AL19" s="300"/>
+      <c r="AM19" s="300"/>
+      <c r="AN19" s="301"/>
     </row>
     <row r="20" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="105" t="s">
@@ -7488,49 +7488,49 @@
       <c r="C20" s="106"/>
       <c r="D20" s="106"/>
       <c r="E20" s="106"/>
-      <c r="F20" s="281"/>
-      <c r="G20" s="281"/>
-      <c r="H20" s="281"/>
-      <c r="I20" s="281"/>
-      <c r="J20" s="281"/>
-      <c r="K20" s="281"/>
-      <c r="L20" s="281"/>
-      <c r="M20" s="281"/>
-      <c r="N20" s="281"/>
-      <c r="O20" s="281"/>
-      <c r="P20" s="286"/>
-      <c r="Q20" s="286"/>
-      <c r="R20" s="286"/>
-      <c r="S20" s="286"/>
-      <c r="T20" s="287"/>
-      <c r="U20" s="286"/>
-      <c r="V20" s="286"/>
-      <c r="W20" s="286"/>
-      <c r="X20" s="286"/>
-      <c r="Y20" s="286"/>
-      <c r="Z20" s="286"/>
-      <c r="AA20" s="286"/>
-      <c r="AB20" s="286"/>
-      <c r="AC20" s="286"/>
-      <c r="AD20" s="286"/>
-      <c r="AE20" s="285" t="s">
+      <c r="F20" s="282"/>
+      <c r="G20" s="282"/>
+      <c r="H20" s="282"/>
+      <c r="I20" s="282"/>
+      <c r="J20" s="282"/>
+      <c r="K20" s="282"/>
+      <c r="L20" s="282"/>
+      <c r="M20" s="282"/>
+      <c r="N20" s="282"/>
+      <c r="O20" s="282"/>
+      <c r="P20" s="287"/>
+      <c r="Q20" s="287"/>
+      <c r="R20" s="287"/>
+      <c r="S20" s="287"/>
+      <c r="T20" s="288"/>
+      <c r="U20" s="287"/>
+      <c r="V20" s="287"/>
+      <c r="W20" s="287"/>
+      <c r="X20" s="287"/>
+      <c r="Y20" s="287"/>
+      <c r="Z20" s="287"/>
+      <c r="AA20" s="287"/>
+      <c r="AB20" s="287"/>
+      <c r="AC20" s="287"/>
+      <c r="AD20" s="287"/>
+      <c r="AE20" s="286" t="s">
         <v>293</v>
       </c>
-      <c r="AF20" s="286"/>
+      <c r="AF20" s="287"/>
       <c r="AG20" s="104"/>
-      <c r="AH20" s="286" t="s">
+      <c r="AH20" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="AI20" s="287"/>
-      <c r="AJ20" s="285" t="s">
+      <c r="AI20" s="288"/>
+      <c r="AJ20" s="286" t="s">
         <v>293</v>
       </c>
-      <c r="AK20" s="286"/>
+      <c r="AK20" s="287"/>
       <c r="AL20" s="107"/>
-      <c r="AM20" s="286" t="s">
+      <c r="AM20" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="AN20" s="287"/>
+      <c r="AN20" s="288"/>
     </row>
     <row r="21" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="108" t="s">
@@ -7550,31 +7550,31 @@
       <c r="M21" s="109"/>
       <c r="N21" s="109"/>
       <c r="O21" s="109"/>
-      <c r="P21" s="307"/>
-      <c r="Q21" s="307"/>
-      <c r="R21" s="307"/>
-      <c r="S21" s="307"/>
-      <c r="T21" s="308"/>
-      <c r="U21" s="307"/>
-      <c r="V21" s="307"/>
-      <c r="W21" s="307"/>
-      <c r="X21" s="307"/>
-      <c r="Y21" s="308"/>
-      <c r="Z21" s="307"/>
-      <c r="AA21" s="307"/>
-      <c r="AB21" s="307"/>
-      <c r="AC21" s="307"/>
-      <c r="AD21" s="308"/>
-      <c r="AE21" s="307"/>
-      <c r="AF21" s="307"/>
-      <c r="AG21" s="307"/>
-      <c r="AH21" s="307"/>
-      <c r="AI21" s="308"/>
-      <c r="AJ21" s="313"/>
-      <c r="AK21" s="307"/>
-      <c r="AL21" s="307"/>
-      <c r="AM21" s="307"/>
-      <c r="AN21" s="308"/>
+      <c r="P21" s="308"/>
+      <c r="Q21" s="308"/>
+      <c r="R21" s="308"/>
+      <c r="S21" s="308"/>
+      <c r="T21" s="309"/>
+      <c r="U21" s="308"/>
+      <c r="V21" s="308"/>
+      <c r="W21" s="308"/>
+      <c r="X21" s="308"/>
+      <c r="Y21" s="309"/>
+      <c r="Z21" s="308"/>
+      <c r="AA21" s="308"/>
+      <c r="AB21" s="308"/>
+      <c r="AC21" s="308"/>
+      <c r="AD21" s="309"/>
+      <c r="AE21" s="308"/>
+      <c r="AF21" s="308"/>
+      <c r="AG21" s="308"/>
+      <c r="AH21" s="308"/>
+      <c r="AI21" s="309"/>
+      <c r="AJ21" s="314"/>
+      <c r="AK21" s="308"/>
+      <c r="AL21" s="308"/>
+      <c r="AM21" s="308"/>
+      <c r="AN21" s="309"/>
     </row>
     <row r="22" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="115" t="s">
@@ -7586,31 +7586,31 @@
       <c r="J22" s="112"/>
       <c r="K22" s="112"/>
       <c r="L22" s="102"/>
-      <c r="P22" s="309"/>
-      <c r="Q22" s="309"/>
-      <c r="R22" s="309"/>
-      <c r="S22" s="309"/>
-      <c r="T22" s="310"/>
-      <c r="U22" s="309"/>
-      <c r="V22" s="309"/>
-      <c r="W22" s="309"/>
-      <c r="X22" s="309"/>
-      <c r="Y22" s="310"/>
-      <c r="Z22" s="309"/>
-      <c r="AA22" s="309"/>
-      <c r="AB22" s="309"/>
-      <c r="AC22" s="309"/>
-      <c r="AD22" s="310"/>
-      <c r="AE22" s="309"/>
-      <c r="AF22" s="309"/>
-      <c r="AG22" s="309"/>
-      <c r="AH22" s="309"/>
-      <c r="AI22" s="310"/>
-      <c r="AJ22" s="314"/>
-      <c r="AK22" s="309"/>
-      <c r="AL22" s="309"/>
-      <c r="AM22" s="309"/>
-      <c r="AN22" s="310"/>
+      <c r="P22" s="310"/>
+      <c r="Q22" s="310"/>
+      <c r="R22" s="310"/>
+      <c r="S22" s="310"/>
+      <c r="T22" s="311"/>
+      <c r="U22" s="310"/>
+      <c r="V22" s="310"/>
+      <c r="W22" s="310"/>
+      <c r="X22" s="310"/>
+      <c r="Y22" s="311"/>
+      <c r="Z22" s="310"/>
+      <c r="AA22" s="310"/>
+      <c r="AB22" s="310"/>
+      <c r="AC22" s="310"/>
+      <c r="AD22" s="311"/>
+      <c r="AE22" s="310"/>
+      <c r="AF22" s="310"/>
+      <c r="AG22" s="310"/>
+      <c r="AH22" s="310"/>
+      <c r="AI22" s="311"/>
+      <c r="AJ22" s="315"/>
+      <c r="AK22" s="310"/>
+      <c r="AL22" s="310"/>
+      <c r="AM22" s="310"/>
+      <c r="AN22" s="311"/>
     </row>
     <row r="23" spans="1:40" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="111" t="s">
@@ -7622,31 +7622,31 @@
       <c r="J23" s="112"/>
       <c r="K23" s="112"/>
       <c r="L23" s="102"/>
-      <c r="P23" s="311"/>
-      <c r="Q23" s="311"/>
-      <c r="R23" s="311"/>
-      <c r="S23" s="311"/>
-      <c r="T23" s="312"/>
-      <c r="U23" s="311"/>
-      <c r="V23" s="311"/>
-      <c r="W23" s="311"/>
-      <c r="X23" s="311"/>
-      <c r="Y23" s="312"/>
-      <c r="Z23" s="311"/>
-      <c r="AA23" s="311"/>
-      <c r="AB23" s="311"/>
-      <c r="AC23" s="311"/>
-      <c r="AD23" s="312"/>
-      <c r="AE23" s="311"/>
-      <c r="AF23" s="311"/>
-      <c r="AG23" s="311"/>
-      <c r="AH23" s="311"/>
-      <c r="AI23" s="312"/>
-      <c r="AJ23" s="315"/>
-      <c r="AK23" s="311"/>
-      <c r="AL23" s="311"/>
-      <c r="AM23" s="311"/>
-      <c r="AN23" s="312"/>
+      <c r="P23" s="312"/>
+      <c r="Q23" s="312"/>
+      <c r="R23" s="312"/>
+      <c r="S23" s="312"/>
+      <c r="T23" s="313"/>
+      <c r="U23" s="312"/>
+      <c r="V23" s="312"/>
+      <c r="W23" s="312"/>
+      <c r="X23" s="312"/>
+      <c r="Y23" s="313"/>
+      <c r="Z23" s="312"/>
+      <c r="AA23" s="312"/>
+      <c r="AB23" s="312"/>
+      <c r="AC23" s="312"/>
+      <c r="AD23" s="313"/>
+      <c r="AE23" s="312"/>
+      <c r="AF23" s="312"/>
+      <c r="AG23" s="312"/>
+      <c r="AH23" s="312"/>
+      <c r="AI23" s="313"/>
+      <c r="AJ23" s="316"/>
+      <c r="AK23" s="312"/>
+      <c r="AL23" s="312"/>
+      <c r="AM23" s="312"/>
+      <c r="AN23" s="313"/>
     </row>
     <row r="24" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="111" t="s">
@@ -7658,31 +7658,31 @@
       <c r="J24" s="112"/>
       <c r="K24" s="112"/>
       <c r="L24" s="102"/>
-      <c r="P24" s="303"/>
-      <c r="Q24" s="302"/>
-      <c r="R24" s="302"/>
-      <c r="S24" s="302"/>
-      <c r="T24" s="302"/>
-      <c r="U24" s="302"/>
-      <c r="V24" s="302"/>
-      <c r="W24" s="302"/>
-      <c r="X24" s="302"/>
-      <c r="Y24" s="302"/>
-      <c r="Z24" s="302"/>
-      <c r="AA24" s="302"/>
-      <c r="AB24" s="302"/>
-      <c r="AC24" s="302"/>
-      <c r="AD24" s="302"/>
-      <c r="AE24" s="302"/>
-      <c r="AF24" s="302"/>
-      <c r="AG24" s="302"/>
-      <c r="AH24" s="302"/>
-      <c r="AI24" s="302"/>
-      <c r="AJ24" s="302"/>
-      <c r="AK24" s="302"/>
-      <c r="AL24" s="302"/>
-      <c r="AM24" s="302"/>
-      <c r="AN24" s="302"/>
+      <c r="P24" s="304"/>
+      <c r="Q24" s="303"/>
+      <c r="R24" s="303"/>
+      <c r="S24" s="303"/>
+      <c r="T24" s="303"/>
+      <c r="U24" s="303"/>
+      <c r="V24" s="303"/>
+      <c r="W24" s="303"/>
+      <c r="X24" s="303"/>
+      <c r="Y24" s="303"/>
+      <c r="Z24" s="303"/>
+      <c r="AA24" s="303"/>
+      <c r="AB24" s="303"/>
+      <c r="AC24" s="303"/>
+      <c r="AD24" s="303"/>
+      <c r="AE24" s="303"/>
+      <c r="AF24" s="303"/>
+      <c r="AG24" s="303"/>
+      <c r="AH24" s="303"/>
+      <c r="AI24" s="303"/>
+      <c r="AJ24" s="303"/>
+      <c r="AK24" s="303"/>
+      <c r="AL24" s="303"/>
+      <c r="AM24" s="303"/>
+      <c r="AN24" s="303"/>
     </row>
     <row r="25" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="113" t="s">
@@ -7702,177 +7702,177 @@
       <c r="M25" s="106"/>
       <c r="N25" s="106"/>
       <c r="O25" s="106"/>
-      <c r="P25" s="303"/>
-      <c r="Q25" s="302"/>
-      <c r="R25" s="302"/>
-      <c r="S25" s="302"/>
-      <c r="T25" s="302"/>
-      <c r="U25" s="302"/>
-      <c r="V25" s="302"/>
-      <c r="W25" s="302"/>
-      <c r="X25" s="302"/>
-      <c r="Y25" s="302"/>
-      <c r="Z25" s="302"/>
-      <c r="AA25" s="302"/>
-      <c r="AB25" s="302"/>
-      <c r="AC25" s="302"/>
-      <c r="AD25" s="302"/>
-      <c r="AE25" s="302"/>
-      <c r="AF25" s="302"/>
-      <c r="AG25" s="302"/>
-      <c r="AH25" s="302"/>
-      <c r="AI25" s="302"/>
-      <c r="AJ25" s="302"/>
-      <c r="AK25" s="302"/>
-      <c r="AL25" s="302"/>
-      <c r="AM25" s="302"/>
-      <c r="AN25" s="302"/>
+      <c r="P25" s="304"/>
+      <c r="Q25" s="303"/>
+      <c r="R25" s="303"/>
+      <c r="S25" s="303"/>
+      <c r="T25" s="303"/>
+      <c r="U25" s="303"/>
+      <c r="V25" s="303"/>
+      <c r="W25" s="303"/>
+      <c r="X25" s="303"/>
+      <c r="Y25" s="303"/>
+      <c r="Z25" s="303"/>
+      <c r="AA25" s="303"/>
+      <c r="AB25" s="303"/>
+      <c r="AC25" s="303"/>
+      <c r="AD25" s="303"/>
+      <c r="AE25" s="303"/>
+      <c r="AF25" s="303"/>
+      <c r="AG25" s="303"/>
+      <c r="AH25" s="303"/>
+      <c r="AI25" s="303"/>
+      <c r="AJ25" s="303"/>
+      <c r="AK25" s="303"/>
+      <c r="AL25" s="303"/>
+      <c r="AM25" s="303"/>
+      <c r="AN25" s="303"/>
     </row>
     <row r="26" spans="1:40" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="306"/>
-      <c r="B26" s="306"/>
-      <c r="C26" s="306"/>
-      <c r="D26" s="306"/>
-      <c r="E26" s="306"/>
-      <c r="F26" s="306"/>
-      <c r="G26" s="306"/>
-      <c r="H26" s="306"/>
-      <c r="I26" s="306"/>
-      <c r="J26" s="306"/>
-      <c r="K26" s="306"/>
-      <c r="L26" s="306"/>
-      <c r="M26" s="306"/>
-      <c r="N26" s="306"/>
-      <c r="O26" s="306"/>
-      <c r="P26" s="306"/>
-      <c r="Q26" s="306"/>
-      <c r="R26" s="306"/>
-      <c r="S26" s="306"/>
-      <c r="T26" s="306"/>
-      <c r="U26" s="306"/>
-      <c r="V26" s="306"/>
-      <c r="W26" s="306"/>
-      <c r="X26" s="306"/>
-      <c r="Y26" s="306"/>
-      <c r="Z26" s="306"/>
-      <c r="AA26" s="306"/>
-      <c r="AB26" s="306"/>
-      <c r="AC26" s="306"/>
-      <c r="AD26" s="306"/>
-      <c r="AE26" s="306"/>
-      <c r="AF26" s="306"/>
-      <c r="AG26" s="306"/>
-      <c r="AH26" s="306"/>
-      <c r="AI26" s="306"/>
-      <c r="AJ26" s="306"/>
-      <c r="AK26" s="306"/>
-      <c r="AL26" s="306"/>
-      <c r="AM26" s="306"/>
-      <c r="AN26" s="306"/>
+      <c r="A26" s="307"/>
+      <c r="B26" s="307"/>
+      <c r="C26" s="307"/>
+      <c r="D26" s="307"/>
+      <c r="E26" s="307"/>
+      <c r="F26" s="307"/>
+      <c r="G26" s="307"/>
+      <c r="H26" s="307"/>
+      <c r="I26" s="307"/>
+      <c r="J26" s="307"/>
+      <c r="K26" s="307"/>
+      <c r="L26" s="307"/>
+      <c r="M26" s="307"/>
+      <c r="N26" s="307"/>
+      <c r="O26" s="307"/>
+      <c r="P26" s="307"/>
+      <c r="Q26" s="307"/>
+      <c r="R26" s="307"/>
+      <c r="S26" s="307"/>
+      <c r="T26" s="307"/>
+      <c r="U26" s="307"/>
+      <c r="V26" s="307"/>
+      <c r="W26" s="307"/>
+      <c r="X26" s="307"/>
+      <c r="Y26" s="307"/>
+      <c r="Z26" s="307"/>
+      <c r="AA26" s="307"/>
+      <c r="AB26" s="307"/>
+      <c r="AC26" s="307"/>
+      <c r="AD26" s="307"/>
+      <c r="AE26" s="307"/>
+      <c r="AF26" s="307"/>
+      <c r="AG26" s="307"/>
+      <c r="AH26" s="307"/>
+      <c r="AI26" s="307"/>
+      <c r="AJ26" s="307"/>
+      <c r="AK26" s="307"/>
+      <c r="AL26" s="307"/>
+      <c r="AM26" s="307"/>
+      <c r="AN26" s="307"/>
     </row>
     <row r="27" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="288" t="s">
+      <c r="A27" s="289" t="s">
         <v>331</v>
       </c>
-      <c r="B27" s="289"/>
-      <c r="C27" s="289"/>
-      <c r="D27" s="289"/>
-      <c r="E27" s="289"/>
-      <c r="F27" s="289"/>
-      <c r="G27" s="289"/>
-      <c r="H27" s="289"/>
-      <c r="I27" s="289"/>
-      <c r="J27" s="289"/>
-      <c r="K27" s="289"/>
+      <c r="B27" s="290"/>
+      <c r="C27" s="290"/>
+      <c r="D27" s="290"/>
+      <c r="E27" s="290"/>
+      <c r="F27" s="290"/>
+      <c r="G27" s="290"/>
+      <c r="H27" s="290"/>
+      <c r="I27" s="290"/>
+      <c r="J27" s="290"/>
+      <c r="K27" s="290"/>
       <c r="L27" s="103"/>
       <c r="M27" s="103"/>
       <c r="N27" s="103"/>
       <c r="O27" s="103"/>
-      <c r="P27" s="292" t="s">
+      <c r="P27" s="293" t="s">
         <v>345</v>
       </c>
-      <c r="Q27" s="293"/>
-      <c r="R27" s="293"/>
-      <c r="S27" s="293"/>
-      <c r="T27" s="294"/>
-      <c r="U27" s="295" t="s">
+      <c r="Q27" s="294"/>
+      <c r="R27" s="294"/>
+      <c r="S27" s="294"/>
+      <c r="T27" s="295"/>
+      <c r="U27" s="296" t="s">
         <v>293</v>
       </c>
-      <c r="V27" s="295"/>
+      <c r="V27" s="296"/>
       <c r="W27" s="104"/>
-      <c r="X27" s="293" t="s">
+      <c r="X27" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="Y27" s="293"/>
-      <c r="Z27" s="296" t="s">
+      <c r="Y27" s="294"/>
+      <c r="Z27" s="297" t="s">
         <v>293</v>
       </c>
-      <c r="AA27" s="295"/>
+      <c r="AA27" s="296"/>
       <c r="AB27" s="104"/>
-      <c r="AC27" s="293" t="s">
+      <c r="AC27" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="AD27" s="294"/>
-      <c r="AE27" s="296" t="s">
+      <c r="AD27" s="295"/>
+      <c r="AE27" s="297" t="s">
         <v>294</v>
       </c>
-      <c r="AF27" s="295"/>
-      <c r="AG27" s="295"/>
-      <c r="AH27" s="295"/>
-      <c r="AI27" s="297"/>
-      <c r="AJ27" s="296" t="s">
+      <c r="AF27" s="296"/>
+      <c r="AG27" s="296"/>
+      <c r="AH27" s="296"/>
+      <c r="AI27" s="298"/>
+      <c r="AJ27" s="297" t="s">
         <v>294</v>
       </c>
-      <c r="AK27" s="295"/>
-      <c r="AL27" s="295"/>
-      <c r="AM27" s="295"/>
-      <c r="AN27" s="297"/>
+      <c r="AK27" s="296"/>
+      <c r="AL27" s="296"/>
+      <c r="AM27" s="296"/>
+      <c r="AN27" s="298"/>
     </row>
     <row r="28" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="290"/>
-      <c r="B28" s="291"/>
-      <c r="C28" s="291"/>
-      <c r="D28" s="291"/>
-      <c r="E28" s="291"/>
-      <c r="F28" s="291"/>
-      <c r="G28" s="291"/>
-      <c r="H28" s="291"/>
-      <c r="I28" s="291"/>
-      <c r="J28" s="291"/>
-      <c r="K28" s="291"/>
+      <c r="A28" s="291"/>
+      <c r="B28" s="292"/>
+      <c r="C28" s="292"/>
+      <c r="D28" s="292"/>
+      <c r="E28" s="292"/>
+      <c r="F28" s="292"/>
+      <c r="G28" s="292"/>
+      <c r="H28" s="292"/>
+      <c r="I28" s="292"/>
+      <c r="J28" s="292"/>
+      <c r="K28" s="292"/>
       <c r="L28" s="101"/>
       <c r="M28" s="101"/>
       <c r="N28" s="101"/>
       <c r="O28" s="101"/>
-      <c r="P28" s="283"/>
-      <c r="Q28" s="283"/>
-      <c r="R28" s="283"/>
-      <c r="S28" s="283"/>
-      <c r="T28" s="284"/>
-      <c r="U28" s="301" t="s">
+      <c r="P28" s="284"/>
+      <c r="Q28" s="284"/>
+      <c r="R28" s="284"/>
+      <c r="S28" s="284"/>
+      <c r="T28" s="285"/>
+      <c r="U28" s="302" t="s">
         <v>346</v>
       </c>
-      <c r="V28" s="283"/>
-      <c r="W28" s="283"/>
-      <c r="X28" s="283"/>
-      <c r="Y28" s="283"/>
-      <c r="Z28" s="301" t="s">
+      <c r="V28" s="284"/>
+      <c r="W28" s="284"/>
+      <c r="X28" s="284"/>
+      <c r="Y28" s="284"/>
+      <c r="Z28" s="302" t="s">
         <v>346</v>
       </c>
-      <c r="AA28" s="283"/>
-      <c r="AB28" s="283"/>
-      <c r="AC28" s="283"/>
-      <c r="AD28" s="283"/>
-      <c r="AE28" s="298"/>
-      <c r="AF28" s="299"/>
-      <c r="AG28" s="299"/>
-      <c r="AH28" s="299"/>
-      <c r="AI28" s="300"/>
-      <c r="AJ28" s="298"/>
-      <c r="AK28" s="299"/>
-      <c r="AL28" s="299"/>
-      <c r="AM28" s="299"/>
-      <c r="AN28" s="300"/>
+      <c r="AA28" s="284"/>
+      <c r="AB28" s="284"/>
+      <c r="AC28" s="284"/>
+      <c r="AD28" s="284"/>
+      <c r="AE28" s="299"/>
+      <c r="AF28" s="300"/>
+      <c r="AG28" s="300"/>
+      <c r="AH28" s="300"/>
+      <c r="AI28" s="301"/>
+      <c r="AJ28" s="299"/>
+      <c r="AK28" s="300"/>
+      <c r="AL28" s="300"/>
+      <c r="AM28" s="300"/>
+      <c r="AN28" s="301"/>
     </row>
     <row r="29" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="105" t="s">
@@ -7882,49 +7882,49 @@
       <c r="C29" s="106"/>
       <c r="D29" s="106"/>
       <c r="E29" s="106"/>
-      <c r="F29" s="281"/>
-      <c r="G29" s="281"/>
-      <c r="H29" s="281"/>
-      <c r="I29" s="281"/>
-      <c r="J29" s="281"/>
-      <c r="K29" s="281"/>
-      <c r="L29" s="281"/>
-      <c r="M29" s="281"/>
-      <c r="N29" s="281"/>
-      <c r="O29" s="281"/>
-      <c r="P29" s="286"/>
-      <c r="Q29" s="286"/>
-      <c r="R29" s="286"/>
-      <c r="S29" s="286"/>
-      <c r="T29" s="287"/>
-      <c r="U29" s="286"/>
-      <c r="V29" s="286"/>
-      <c r="W29" s="286"/>
-      <c r="X29" s="286"/>
-      <c r="Y29" s="286"/>
-      <c r="Z29" s="286"/>
-      <c r="AA29" s="286"/>
-      <c r="AB29" s="286"/>
-      <c r="AC29" s="286"/>
-      <c r="AD29" s="286"/>
-      <c r="AE29" s="285" t="s">
+      <c r="F29" s="282"/>
+      <c r="G29" s="282"/>
+      <c r="H29" s="282"/>
+      <c r="I29" s="282"/>
+      <c r="J29" s="282"/>
+      <c r="K29" s="282"/>
+      <c r="L29" s="282"/>
+      <c r="M29" s="282"/>
+      <c r="N29" s="282"/>
+      <c r="O29" s="282"/>
+      <c r="P29" s="287"/>
+      <c r="Q29" s="287"/>
+      <c r="R29" s="287"/>
+      <c r="S29" s="287"/>
+      <c r="T29" s="288"/>
+      <c r="U29" s="287"/>
+      <c r="V29" s="287"/>
+      <c r="W29" s="287"/>
+      <c r="X29" s="287"/>
+      <c r="Y29" s="287"/>
+      <c r="Z29" s="287"/>
+      <c r="AA29" s="287"/>
+      <c r="AB29" s="287"/>
+      <c r="AC29" s="287"/>
+      <c r="AD29" s="287"/>
+      <c r="AE29" s="286" t="s">
         <v>293</v>
       </c>
-      <c r="AF29" s="286"/>
+      <c r="AF29" s="287"/>
       <c r="AG29" s="104"/>
-      <c r="AH29" s="286" t="s">
+      <c r="AH29" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="AI29" s="287"/>
-      <c r="AJ29" s="285" t="s">
+      <c r="AI29" s="288"/>
+      <c r="AJ29" s="286" t="s">
         <v>293</v>
       </c>
-      <c r="AK29" s="286"/>
+      <c r="AK29" s="287"/>
       <c r="AL29" s="107"/>
-      <c r="AM29" s="286" t="s">
+      <c r="AM29" s="287" t="s">
         <v>31</v>
       </c>
-      <c r="AN29" s="287"/>
+      <c r="AN29" s="288"/>
     </row>
     <row r="30" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="108" t="s">
@@ -7939,36 +7939,36 @@
       <c r="H30" s="110"/>
       <c r="I30" s="110"/>
       <c r="J30" s="110"/>
-      <c r="K30" s="304"/>
-      <c r="L30" s="304"/>
-      <c r="M30" s="304"/>
-      <c r="N30" s="304"/>
-      <c r="O30" s="304"/>
-      <c r="P30" s="303"/>
-      <c r="Q30" s="302"/>
-      <c r="R30" s="302"/>
-      <c r="S30" s="302"/>
-      <c r="T30" s="302"/>
-      <c r="U30" s="302"/>
-      <c r="V30" s="302"/>
-      <c r="W30" s="302"/>
-      <c r="X30" s="302"/>
-      <c r="Y30" s="302"/>
-      <c r="Z30" s="302"/>
-      <c r="AA30" s="302"/>
-      <c r="AB30" s="302"/>
-      <c r="AC30" s="302"/>
-      <c r="AD30" s="302"/>
-      <c r="AE30" s="302"/>
-      <c r="AF30" s="302"/>
-      <c r="AG30" s="302"/>
-      <c r="AH30" s="302"/>
-      <c r="AI30" s="302"/>
-      <c r="AJ30" s="302"/>
-      <c r="AK30" s="302"/>
-      <c r="AL30" s="302"/>
-      <c r="AM30" s="302"/>
-      <c r="AN30" s="302"/>
+      <c r="K30" s="305"/>
+      <c r="L30" s="305"/>
+      <c r="M30" s="305"/>
+      <c r="N30" s="305"/>
+      <c r="O30" s="305"/>
+      <c r="P30" s="304"/>
+      <c r="Q30" s="303"/>
+      <c r="R30" s="303"/>
+      <c r="S30" s="303"/>
+      <c r="T30" s="303"/>
+      <c r="U30" s="303"/>
+      <c r="V30" s="303"/>
+      <c r="W30" s="303"/>
+      <c r="X30" s="303"/>
+      <c r="Y30" s="303"/>
+      <c r="Z30" s="303"/>
+      <c r="AA30" s="303"/>
+      <c r="AB30" s="303"/>
+      <c r="AC30" s="303"/>
+      <c r="AD30" s="303"/>
+      <c r="AE30" s="303"/>
+      <c r="AF30" s="303"/>
+      <c r="AG30" s="303"/>
+      <c r="AH30" s="303"/>
+      <c r="AI30" s="303"/>
+      <c r="AJ30" s="303"/>
+      <c r="AK30" s="303"/>
+      <c r="AL30" s="303"/>
+      <c r="AM30" s="303"/>
+      <c r="AN30" s="303"/>
     </row>
     <row r="31" spans="1:40" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="111" t="s">
@@ -7978,36 +7978,36 @@
       <c r="H31" s="112"/>
       <c r="I31" s="112"/>
       <c r="J31" s="112"/>
-      <c r="K31" s="305"/>
-      <c r="L31" s="305"/>
-      <c r="M31" s="305"/>
-      <c r="N31" s="305"/>
-      <c r="O31" s="305"/>
-      <c r="P31" s="303"/>
-      <c r="Q31" s="302"/>
-      <c r="R31" s="302"/>
-      <c r="S31" s="302"/>
-      <c r="T31" s="302"/>
-      <c r="U31" s="302"/>
-      <c r="V31" s="302"/>
-      <c r="W31" s="302"/>
-      <c r="X31" s="302"/>
-      <c r="Y31" s="302"/>
-      <c r="Z31" s="302"/>
-      <c r="AA31" s="302"/>
-      <c r="AB31" s="302"/>
-      <c r="AC31" s="302"/>
-      <c r="AD31" s="302"/>
-      <c r="AE31" s="302"/>
-      <c r="AF31" s="302"/>
-      <c r="AG31" s="302"/>
-      <c r="AH31" s="302"/>
-      <c r="AI31" s="302"/>
-      <c r="AJ31" s="302"/>
-      <c r="AK31" s="302"/>
-      <c r="AL31" s="302"/>
-      <c r="AM31" s="302"/>
-      <c r="AN31" s="302"/>
+      <c r="K31" s="306"/>
+      <c r="L31" s="306"/>
+      <c r="M31" s="306"/>
+      <c r="N31" s="306"/>
+      <c r="O31" s="306"/>
+      <c r="P31" s="304"/>
+      <c r="Q31" s="303"/>
+      <c r="R31" s="303"/>
+      <c r="S31" s="303"/>
+      <c r="T31" s="303"/>
+      <c r="U31" s="303"/>
+      <c r="V31" s="303"/>
+      <c r="W31" s="303"/>
+      <c r="X31" s="303"/>
+      <c r="Y31" s="303"/>
+      <c r="Z31" s="303"/>
+      <c r="AA31" s="303"/>
+      <c r="AB31" s="303"/>
+      <c r="AC31" s="303"/>
+      <c r="AD31" s="303"/>
+      <c r="AE31" s="303"/>
+      <c r="AF31" s="303"/>
+      <c r="AG31" s="303"/>
+      <c r="AH31" s="303"/>
+      <c r="AI31" s="303"/>
+      <c r="AJ31" s="303"/>
+      <c r="AK31" s="303"/>
+      <c r="AL31" s="303"/>
+      <c r="AM31" s="303"/>
+      <c r="AN31" s="303"/>
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A32" s="111" t="s">
@@ -8017,36 +8017,36 @@
       <c r="H32" s="112"/>
       <c r="I32" s="112"/>
       <c r="J32" s="112"/>
-      <c r="K32" s="305"/>
-      <c r="L32" s="305"/>
-      <c r="M32" s="305"/>
-      <c r="N32" s="305"/>
-      <c r="O32" s="305"/>
-      <c r="P32" s="303"/>
-      <c r="Q32" s="302"/>
-      <c r="R32" s="302"/>
-      <c r="S32" s="302"/>
-      <c r="T32" s="302"/>
-      <c r="U32" s="302"/>
-      <c r="V32" s="302"/>
-      <c r="W32" s="302"/>
-      <c r="X32" s="302"/>
-      <c r="Y32" s="302"/>
-      <c r="Z32" s="302"/>
-      <c r="AA32" s="302"/>
-      <c r="AB32" s="302"/>
-      <c r="AC32" s="302"/>
-      <c r="AD32" s="302"/>
-      <c r="AE32" s="302"/>
-      <c r="AF32" s="302"/>
-      <c r="AG32" s="302"/>
-      <c r="AH32" s="302"/>
-      <c r="AI32" s="302"/>
-      <c r="AJ32" s="302"/>
-      <c r="AK32" s="302"/>
-      <c r="AL32" s="302"/>
-      <c r="AM32" s="302"/>
-      <c r="AN32" s="302"/>
+      <c r="K32" s="306"/>
+      <c r="L32" s="306"/>
+      <c r="M32" s="306"/>
+      <c r="N32" s="306"/>
+      <c r="O32" s="306"/>
+      <c r="P32" s="304"/>
+      <c r="Q32" s="303"/>
+      <c r="R32" s="303"/>
+      <c r="S32" s="303"/>
+      <c r="T32" s="303"/>
+      <c r="U32" s="303"/>
+      <c r="V32" s="303"/>
+      <c r="W32" s="303"/>
+      <c r="X32" s="303"/>
+      <c r="Y32" s="303"/>
+      <c r="Z32" s="303"/>
+      <c r="AA32" s="303"/>
+      <c r="AB32" s="303"/>
+      <c r="AC32" s="303"/>
+      <c r="AD32" s="303"/>
+      <c r="AE32" s="303"/>
+      <c r="AF32" s="303"/>
+      <c r="AG32" s="303"/>
+      <c r="AH32" s="303"/>
+      <c r="AI32" s="303"/>
+      <c r="AJ32" s="303"/>
+      <c r="AK32" s="303"/>
+      <c r="AL32" s="303"/>
+      <c r="AM32" s="303"/>
+      <c r="AN32" s="303"/>
     </row>
     <row r="33" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A33" s="111" t="s">
@@ -8056,36 +8056,36 @@
       <c r="H33" s="112"/>
       <c r="I33" s="112"/>
       <c r="J33" s="112"/>
-      <c r="K33" s="305"/>
-      <c r="L33" s="305"/>
-      <c r="M33" s="305"/>
-      <c r="N33" s="305"/>
-      <c r="O33" s="305"/>
-      <c r="P33" s="303"/>
-      <c r="Q33" s="302"/>
-      <c r="R33" s="302"/>
-      <c r="S33" s="302"/>
-      <c r="T33" s="302"/>
-      <c r="U33" s="302"/>
-      <c r="V33" s="302"/>
-      <c r="W33" s="302"/>
-      <c r="X33" s="302"/>
-      <c r="Y33" s="302"/>
-      <c r="Z33" s="302"/>
-      <c r="AA33" s="302"/>
-      <c r="AB33" s="302"/>
-      <c r="AC33" s="302"/>
-      <c r="AD33" s="302"/>
-      <c r="AE33" s="302"/>
-      <c r="AF33" s="302"/>
-      <c r="AG33" s="302"/>
-      <c r="AH33" s="302"/>
-      <c r="AI33" s="302"/>
-      <c r="AJ33" s="302"/>
-      <c r="AK33" s="302"/>
-      <c r="AL33" s="302"/>
-      <c r="AM33" s="302"/>
-      <c r="AN33" s="302"/>
+      <c r="K33" s="306"/>
+      <c r="L33" s="306"/>
+      <c r="M33" s="306"/>
+      <c r="N33" s="306"/>
+      <c r="O33" s="306"/>
+      <c r="P33" s="304"/>
+      <c r="Q33" s="303"/>
+      <c r="R33" s="303"/>
+      <c r="S33" s="303"/>
+      <c r="T33" s="303"/>
+      <c r="U33" s="303"/>
+      <c r="V33" s="303"/>
+      <c r="W33" s="303"/>
+      <c r="X33" s="303"/>
+      <c r="Y33" s="303"/>
+      <c r="Z33" s="303"/>
+      <c r="AA33" s="303"/>
+      <c r="AB33" s="303"/>
+      <c r="AC33" s="303"/>
+      <c r="AD33" s="303"/>
+      <c r="AE33" s="303"/>
+      <c r="AF33" s="303"/>
+      <c r="AG33" s="303"/>
+      <c r="AH33" s="303"/>
+      <c r="AI33" s="303"/>
+      <c r="AJ33" s="303"/>
+      <c r="AK33" s="303"/>
+      <c r="AL33" s="303"/>
+      <c r="AM33" s="303"/>
+      <c r="AN33" s="303"/>
     </row>
     <row r="34" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A34" s="111" t="s">
@@ -8095,36 +8095,36 @@
       <c r="H34" s="112"/>
       <c r="I34" s="112"/>
       <c r="J34" s="112"/>
-      <c r="K34" s="305"/>
-      <c r="L34" s="305"/>
-      <c r="M34" s="305"/>
-      <c r="N34" s="305"/>
-      <c r="O34" s="305"/>
-      <c r="P34" s="303"/>
-      <c r="Q34" s="302"/>
-      <c r="R34" s="302"/>
-      <c r="S34" s="302"/>
-      <c r="T34" s="302"/>
-      <c r="U34" s="302"/>
-      <c r="V34" s="302"/>
-      <c r="W34" s="302"/>
-      <c r="X34" s="302"/>
-      <c r="Y34" s="302"/>
-      <c r="Z34" s="302"/>
-      <c r="AA34" s="302"/>
-      <c r="AB34" s="302"/>
-      <c r="AC34" s="302"/>
-      <c r="AD34" s="302"/>
-      <c r="AE34" s="302"/>
-      <c r="AF34" s="302"/>
-      <c r="AG34" s="302"/>
-      <c r="AH34" s="302"/>
-      <c r="AI34" s="302"/>
-      <c r="AJ34" s="302"/>
-      <c r="AK34" s="302"/>
-      <c r="AL34" s="302"/>
-      <c r="AM34" s="302"/>
-      <c r="AN34" s="302"/>
+      <c r="K34" s="306"/>
+      <c r="L34" s="306"/>
+      <c r="M34" s="306"/>
+      <c r="N34" s="306"/>
+      <c r="O34" s="306"/>
+      <c r="P34" s="304"/>
+      <c r="Q34" s="303"/>
+      <c r="R34" s="303"/>
+      <c r="S34" s="303"/>
+      <c r="T34" s="303"/>
+      <c r="U34" s="303"/>
+      <c r="V34" s="303"/>
+      <c r="W34" s="303"/>
+      <c r="X34" s="303"/>
+      <c r="Y34" s="303"/>
+      <c r="Z34" s="303"/>
+      <c r="AA34" s="303"/>
+      <c r="AB34" s="303"/>
+      <c r="AC34" s="303"/>
+      <c r="AD34" s="303"/>
+      <c r="AE34" s="303"/>
+      <c r="AF34" s="303"/>
+      <c r="AG34" s="303"/>
+      <c r="AH34" s="303"/>
+      <c r="AI34" s="303"/>
+      <c r="AJ34" s="303"/>
+      <c r="AK34" s="303"/>
+      <c r="AL34" s="303"/>
+      <c r="AM34" s="303"/>
+      <c r="AN34" s="303"/>
     </row>
     <row r="35" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A35" s="113" t="s">
@@ -8139,36 +8139,36 @@
       <c r="H35" s="100"/>
       <c r="I35" s="100"/>
       <c r="J35" s="100"/>
-      <c r="K35" s="281"/>
-      <c r="L35" s="281"/>
-      <c r="M35" s="281"/>
-      <c r="N35" s="281"/>
-      <c r="O35" s="281"/>
-      <c r="P35" s="303"/>
-      <c r="Q35" s="302"/>
-      <c r="R35" s="302"/>
-      <c r="S35" s="302"/>
-      <c r="T35" s="302"/>
-      <c r="U35" s="302"/>
-      <c r="V35" s="302"/>
-      <c r="W35" s="302"/>
-      <c r="X35" s="302"/>
-      <c r="Y35" s="302"/>
-      <c r="Z35" s="302"/>
-      <c r="AA35" s="302"/>
-      <c r="AB35" s="302"/>
-      <c r="AC35" s="302"/>
-      <c r="AD35" s="302"/>
-      <c r="AE35" s="302"/>
-      <c r="AF35" s="302"/>
-      <c r="AG35" s="302"/>
-      <c r="AH35" s="302"/>
-      <c r="AI35" s="302"/>
-      <c r="AJ35" s="302"/>
-      <c r="AK35" s="302"/>
-      <c r="AL35" s="302"/>
-      <c r="AM35" s="302"/>
-      <c r="AN35" s="302"/>
+      <c r="K35" s="282"/>
+      <c r="L35" s="282"/>
+      <c r="M35" s="282"/>
+      <c r="N35" s="282"/>
+      <c r="O35" s="282"/>
+      <c r="P35" s="304"/>
+      <c r="Q35" s="303"/>
+      <c r="R35" s="303"/>
+      <c r="S35" s="303"/>
+      <c r="T35" s="303"/>
+      <c r="U35" s="303"/>
+      <c r="V35" s="303"/>
+      <c r="W35" s="303"/>
+      <c r="X35" s="303"/>
+      <c r="Y35" s="303"/>
+      <c r="Z35" s="303"/>
+      <c r="AA35" s="303"/>
+      <c r="AB35" s="303"/>
+      <c r="AC35" s="303"/>
+      <c r="AD35" s="303"/>
+      <c r="AE35" s="303"/>
+      <c r="AF35" s="303"/>
+      <c r="AG35" s="303"/>
+      <c r="AH35" s="303"/>
+      <c r="AI35" s="303"/>
+      <c r="AJ35" s="303"/>
+      <c r="AK35" s="303"/>
+      <c r="AL35" s="303"/>
+      <c r="AM35" s="303"/>
+      <c r="AN35" s="303"/>
     </row>
     <row r="36" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A36" s="101"/>
@@ -8566,32 +8566,32 @@
       <c r="T47" s="173"/>
       <c r="U47" s="173"/>
       <c r="V47" s="173"/>
-      <c r="W47" s="262" t="s">
+      <c r="W47" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="X47" s="263"/>
-      <c r="Y47" s="263"/>
-      <c r="Z47" s="350"/>
-      <c r="AA47" s="350"/>
-      <c r="AB47" s="260" t="s">
+      <c r="X47" s="264"/>
+      <c r="Y47" s="264"/>
+      <c r="Z47" s="260"/>
+      <c r="AA47" s="260"/>
+      <c r="AB47" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="AC47" s="260"/>
-      <c r="AD47" s="260"/>
-      <c r="AE47" s="261"/>
-      <c r="AF47" s="262" t="s">
+      <c r="AC47" s="261"/>
+      <c r="AD47" s="261"/>
+      <c r="AE47" s="262"/>
+      <c r="AF47" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="AG47" s="263"/>
-      <c r="AH47" s="263"/>
-      <c r="AI47" s="350"/>
-      <c r="AJ47" s="350"/>
-      <c r="AK47" s="260" t="s">
+      <c r="AG47" s="264"/>
+      <c r="AH47" s="264"/>
+      <c r="AI47" s="260"/>
+      <c r="AJ47" s="260"/>
+      <c r="AK47" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="AL47" s="260"/>
-      <c r="AM47" s="260"/>
-      <c r="AN47" s="261"/>
+      <c r="AL47" s="261"/>
+      <c r="AM47" s="261"/>
+      <c r="AN47" s="262"/>
     </row>
     <row r="48" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A48" s="191"/>
@@ -9151,46 +9151,46 @@
       <c r="AX4" s="183"/>
       <c r="AY4" s="183"/>
       <c r="AZ4" s="183"/>
-      <c r="BA4" s="225"/>
-      <c r="BB4" s="225"/>
-      <c r="BC4" s="225"/>
-      <c r="BD4" s="225"/>
-      <c r="BE4" s="225"/>
-      <c r="BF4" s="225"/>
-      <c r="BG4" s="225"/>
-      <c r="BH4" s="225"/>
-      <c r="BI4" s="318"/>
-      <c r="BJ4" s="225"/>
-      <c r="BK4" s="225"/>
-      <c r="BL4" s="225"/>
-      <c r="BM4" s="225"/>
-      <c r="BN4" s="225"/>
-      <c r="BO4" s="225"/>
-      <c r="BP4" s="225"/>
-      <c r="BQ4" s="225"/>
-      <c r="BR4" s="225"/>
-      <c r="BS4" s="225"/>
-      <c r="BT4" s="225"/>
-      <c r="BU4" s="225"/>
-      <c r="BV4" s="225"/>
-      <c r="BW4" s="225"/>
-      <c r="BX4" s="225"/>
-      <c r="BY4" s="225"/>
-      <c r="BZ4" s="225"/>
-      <c r="CA4" s="225"/>
+      <c r="BA4" s="226"/>
+      <c r="BB4" s="226"/>
+      <c r="BC4" s="226"/>
+      <c r="BD4" s="226"/>
+      <c r="BE4" s="226"/>
+      <c r="BF4" s="226"/>
+      <c r="BG4" s="226"/>
+      <c r="BH4" s="226"/>
+      <c r="BI4" s="319"/>
+      <c r="BJ4" s="226"/>
+      <c r="BK4" s="226"/>
+      <c r="BL4" s="226"/>
+      <c r="BM4" s="226"/>
+      <c r="BN4" s="226"/>
+      <c r="BO4" s="226"/>
+      <c r="BP4" s="226"/>
+      <c r="BQ4" s="226"/>
+      <c r="BR4" s="226"/>
+      <c r="BS4" s="226"/>
+      <c r="BT4" s="226"/>
+      <c r="BU4" s="226"/>
+      <c r="BV4" s="226"/>
+      <c r="BW4" s="226"/>
+      <c r="BX4" s="226"/>
+      <c r="BY4" s="226"/>
+      <c r="BZ4" s="226"/>
+      <c r="CA4" s="226"/>
     </row>
     <row r="5" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR5" s="317" t="s">
+      <c r="AR5" s="318" t="s">
         <v>208</v>
       </c>
-      <c r="AS5" s="317"/>
-      <c r="AT5" s="317"/>
-      <c r="AU5" s="317"/>
-      <c r="AV5" s="317"/>
-      <c r="AW5" s="317"/>
-      <c r="AX5" s="317"/>
-      <c r="AY5" s="317"/>
-      <c r="AZ5" s="317"/>
+      <c r="AS5" s="318"/>
+      <c r="AT5" s="318"/>
+      <c r="AU5" s="318"/>
+      <c r="AV5" s="318"/>
+      <c r="AW5" s="318"/>
+      <c r="AX5" s="318"/>
+      <c r="AY5" s="318"/>
+      <c r="AZ5" s="318"/>
       <c r="BA5" s="173"/>
       <c r="BB5" s="173"/>
       <c r="BC5" s="173"/>
@@ -9220,17 +9220,17 @@
       <c r="CA5" s="173"/>
     </row>
     <row r="6" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR6" s="317" t="s">
+      <c r="AR6" s="318" t="s">
         <v>209</v>
       </c>
-      <c r="AS6" s="317"/>
-      <c r="AT6" s="317"/>
-      <c r="AU6" s="317"/>
-      <c r="AV6" s="317"/>
-      <c r="AW6" s="317"/>
-      <c r="AX6" s="317"/>
-      <c r="AY6" s="317"/>
-      <c r="AZ6" s="317"/>
+      <c r="AS6" s="318"/>
+      <c r="AT6" s="318"/>
+      <c r="AU6" s="318"/>
+      <c r="AV6" s="318"/>
+      <c r="AW6" s="318"/>
+      <c r="AX6" s="318"/>
+      <c r="AY6" s="318"/>
+      <c r="AZ6" s="318"/>
       <c r="BA6" s="173"/>
       <c r="BB6" s="173"/>
       <c r="BC6" s="173"/>
@@ -9371,10 +9371,10 @@
       <c r="CA9" s="173"/>
     </row>
     <row r="10" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR10" s="225"/>
-      <c r="AS10" s="225"/>
-      <c r="AT10" s="225"/>
-      <c r="AU10" s="225"/>
+      <c r="AR10" s="226"/>
+      <c r="AS10" s="226"/>
+      <c r="AT10" s="226"/>
+      <c r="AU10" s="226"/>
       <c r="AV10" s="259" t="s">
         <v>210</v>
       </c>
@@ -9405,18 +9405,18 @@
       <c r="BS10" s="173"/>
       <c r="BT10" s="173"/>
       <c r="BU10" s="173"/>
-      <c r="BV10" s="225"/>
-      <c r="BW10" s="225"/>
-      <c r="BX10" s="225"/>
-      <c r="BY10" s="225"/>
-      <c r="BZ10" s="225"/>
-      <c r="CA10" s="225"/>
+      <c r="BV10" s="226"/>
+      <c r="BW10" s="226"/>
+      <c r="BX10" s="226"/>
+      <c r="BY10" s="226"/>
+      <c r="BZ10" s="226"/>
+      <c r="CA10" s="226"/>
     </row>
     <row r="11" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR11" s="225"/>
-      <c r="AS11" s="225"/>
-      <c r="AT11" s="225"/>
-      <c r="AU11" s="225"/>
+      <c r="AR11" s="226"/>
+      <c r="AS11" s="226"/>
+      <c r="AT11" s="226"/>
+      <c r="AU11" s="226"/>
       <c r="AV11" s="173"/>
       <c r="AW11" s="173"/>
       <c r="AX11" s="173"/>
@@ -9445,18 +9445,18 @@
       <c r="BS11" s="173"/>
       <c r="BT11" s="173"/>
       <c r="BU11" s="173"/>
-      <c r="BV11" s="225"/>
-      <c r="BW11" s="225"/>
-      <c r="BX11" s="225"/>
-      <c r="BY11" s="225"/>
-      <c r="BZ11" s="225"/>
-      <c r="CA11" s="225"/>
+      <c r="BV11" s="226"/>
+      <c r="BW11" s="226"/>
+      <c r="BX11" s="226"/>
+      <c r="BY11" s="226"/>
+      <c r="BZ11" s="226"/>
+      <c r="CA11" s="226"/>
     </row>
     <row r="12" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR12" s="225"/>
-      <c r="AS12" s="225"/>
-      <c r="AT12" s="225"/>
-      <c r="AU12" s="225"/>
+      <c r="AR12" s="226"/>
+      <c r="AS12" s="226"/>
+      <c r="AT12" s="226"/>
+      <c r="AU12" s="226"/>
       <c r="AV12" s="259" t="s">
         <v>211</v>
       </c>
@@ -9487,18 +9487,18 @@
       <c r="BS12" s="173"/>
       <c r="BT12" s="173"/>
       <c r="BU12" s="173"/>
-      <c r="BV12" s="225"/>
-      <c r="BW12" s="225"/>
-      <c r="BX12" s="225"/>
-      <c r="BY12" s="225"/>
-      <c r="BZ12" s="225"/>
-      <c r="CA12" s="225"/>
+      <c r="BV12" s="226"/>
+      <c r="BW12" s="226"/>
+      <c r="BX12" s="226"/>
+      <c r="BY12" s="226"/>
+      <c r="BZ12" s="226"/>
+      <c r="CA12" s="226"/>
     </row>
     <row r="13" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR13" s="225"/>
-      <c r="AS13" s="225"/>
-      <c r="AT13" s="225"/>
-      <c r="AU13" s="225"/>
+      <c r="AR13" s="226"/>
+      <c r="AS13" s="226"/>
+      <c r="AT13" s="226"/>
+      <c r="AU13" s="226"/>
       <c r="AV13" s="173"/>
       <c r="AW13" s="173"/>
       <c r="AX13" s="173"/>
@@ -9527,18 +9527,18 @@
       <c r="BS13" s="173"/>
       <c r="BT13" s="173"/>
       <c r="BU13" s="173"/>
-      <c r="BV13" s="225"/>
-      <c r="BW13" s="225"/>
-      <c r="BX13" s="225"/>
-      <c r="BY13" s="225"/>
-      <c r="BZ13" s="225"/>
-      <c r="CA13" s="225"/>
+      <c r="BV13" s="226"/>
+      <c r="BW13" s="226"/>
+      <c r="BX13" s="226"/>
+      <c r="BY13" s="226"/>
+      <c r="BZ13" s="226"/>
+      <c r="CA13" s="226"/>
     </row>
     <row r="14" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR14" s="225"/>
-      <c r="AS14" s="225"/>
-      <c r="AT14" s="225"/>
-      <c r="AU14" s="225"/>
+      <c r="AR14" s="226"/>
+      <c r="AS14" s="226"/>
+      <c r="AT14" s="226"/>
+      <c r="AU14" s="226"/>
       <c r="AV14" s="259" t="s">
         <v>210</v>
       </c>
@@ -9569,18 +9569,18 @@
       <c r="BS14" s="173"/>
       <c r="BT14" s="173"/>
       <c r="BU14" s="173"/>
-      <c r="BV14" s="225"/>
-      <c r="BW14" s="225"/>
-      <c r="BX14" s="225"/>
-      <c r="BY14" s="225"/>
-      <c r="BZ14" s="225"/>
-      <c r="CA14" s="225"/>
+      <c r="BV14" s="226"/>
+      <c r="BW14" s="226"/>
+      <c r="BX14" s="226"/>
+      <c r="BY14" s="226"/>
+      <c r="BZ14" s="226"/>
+      <c r="CA14" s="226"/>
     </row>
     <row r="15" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR15" s="225"/>
-      <c r="AS15" s="225"/>
-      <c r="AT15" s="225"/>
-      <c r="AU15" s="225"/>
+      <c r="AR15" s="226"/>
+      <c r="AS15" s="226"/>
+      <c r="AT15" s="226"/>
+      <c r="AU15" s="226"/>
       <c r="AV15" s="173"/>
       <c r="AW15" s="173"/>
       <c r="AX15" s="173"/>
@@ -9609,18 +9609,18 @@
       <c r="BS15" s="173"/>
       <c r="BT15" s="173"/>
       <c r="BU15" s="173"/>
-      <c r="BV15" s="225"/>
-      <c r="BW15" s="225"/>
-      <c r="BX15" s="225"/>
-      <c r="BY15" s="225"/>
-      <c r="BZ15" s="225"/>
-      <c r="CA15" s="225"/>
+      <c r="BV15" s="226"/>
+      <c r="BW15" s="226"/>
+      <c r="BX15" s="226"/>
+      <c r="BY15" s="226"/>
+      <c r="BZ15" s="226"/>
+      <c r="CA15" s="226"/>
     </row>
     <row r="16" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR16" s="225"/>
-      <c r="AS16" s="225"/>
-      <c r="AT16" s="225"/>
-      <c r="AU16" s="225"/>
+      <c r="AR16" s="226"/>
+      <c r="AS16" s="226"/>
+      <c r="AT16" s="226"/>
+      <c r="AU16" s="226"/>
       <c r="AV16" s="259" t="s">
         <v>211</v>
       </c>
@@ -9651,18 +9651,18 @@
       <c r="BS16" s="173"/>
       <c r="BT16" s="173"/>
       <c r="BU16" s="173"/>
-      <c r="BV16" s="225"/>
-      <c r="BW16" s="225"/>
-      <c r="BX16" s="225"/>
-      <c r="BY16" s="225"/>
-      <c r="BZ16" s="225"/>
-      <c r="CA16" s="225"/>
+      <c r="BV16" s="226"/>
+      <c r="BW16" s="226"/>
+      <c r="BX16" s="226"/>
+      <c r="BY16" s="226"/>
+      <c r="BZ16" s="226"/>
+      <c r="CA16" s="226"/>
     </row>
     <row r="17" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR17" s="225"/>
-      <c r="AS17" s="225"/>
-      <c r="AT17" s="225"/>
-      <c r="AU17" s="225"/>
+      <c r="AR17" s="226"/>
+      <c r="AS17" s="226"/>
+      <c r="AT17" s="226"/>
+      <c r="AU17" s="226"/>
       <c r="AV17" s="173"/>
       <c r="AW17" s="173"/>
       <c r="AX17" s="173"/>
@@ -9691,18 +9691,18 @@
       <c r="BS17" s="173"/>
       <c r="BT17" s="173"/>
       <c r="BU17" s="173"/>
-      <c r="BV17" s="225"/>
-      <c r="BW17" s="225"/>
-      <c r="BX17" s="225"/>
-      <c r="BY17" s="225"/>
-      <c r="BZ17" s="225"/>
-      <c r="CA17" s="225"/>
+      <c r="BV17" s="226"/>
+      <c r="BW17" s="226"/>
+      <c r="BX17" s="226"/>
+      <c r="BY17" s="226"/>
+      <c r="BZ17" s="226"/>
+      <c r="CA17" s="226"/>
     </row>
     <row r="18" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR18" s="225"/>
-      <c r="AS18" s="225"/>
-      <c r="AT18" s="225"/>
-      <c r="AU18" s="225"/>
+      <c r="AR18" s="226"/>
+      <c r="AS18" s="226"/>
+      <c r="AT18" s="226"/>
+      <c r="AU18" s="226"/>
       <c r="AV18" s="259" t="s">
         <v>210</v>
       </c>
@@ -9733,18 +9733,18 @@
       <c r="BS18" s="173"/>
       <c r="BT18" s="173"/>
       <c r="BU18" s="173"/>
-      <c r="BV18" s="225"/>
-      <c r="BW18" s="225"/>
-      <c r="BX18" s="225"/>
-      <c r="BY18" s="225"/>
-      <c r="BZ18" s="225"/>
-      <c r="CA18" s="225"/>
+      <c r="BV18" s="226"/>
+      <c r="BW18" s="226"/>
+      <c r="BX18" s="226"/>
+      <c r="BY18" s="226"/>
+      <c r="BZ18" s="226"/>
+      <c r="CA18" s="226"/>
     </row>
     <row r="19" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR19" s="225"/>
-      <c r="AS19" s="225"/>
-      <c r="AT19" s="225"/>
-      <c r="AU19" s="225"/>
+      <c r="AR19" s="226"/>
+      <c r="AS19" s="226"/>
+      <c r="AT19" s="226"/>
+      <c r="AU19" s="226"/>
       <c r="AV19" s="173"/>
       <c r="AW19" s="173"/>
       <c r="AX19" s="173"/>
@@ -9773,18 +9773,18 @@
       <c r="BS19" s="173"/>
       <c r="BT19" s="173"/>
       <c r="BU19" s="173"/>
-      <c r="BV19" s="225"/>
-      <c r="BW19" s="225"/>
-      <c r="BX19" s="225"/>
-      <c r="BY19" s="225"/>
-      <c r="BZ19" s="225"/>
-      <c r="CA19" s="225"/>
+      <c r="BV19" s="226"/>
+      <c r="BW19" s="226"/>
+      <c r="BX19" s="226"/>
+      <c r="BY19" s="226"/>
+      <c r="BZ19" s="226"/>
+      <c r="CA19" s="226"/>
     </row>
     <row r="20" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR20" s="225"/>
-      <c r="AS20" s="225"/>
-      <c r="AT20" s="225"/>
-      <c r="AU20" s="225"/>
+      <c r="AR20" s="226"/>
+      <c r="AS20" s="226"/>
+      <c r="AT20" s="226"/>
+      <c r="AU20" s="226"/>
       <c r="AV20" s="259" t="s">
         <v>211</v>
       </c>
@@ -9815,18 +9815,18 @@
       <c r="BS20" s="173"/>
       <c r="BT20" s="173"/>
       <c r="BU20" s="173"/>
-      <c r="BV20" s="225"/>
-      <c r="BW20" s="225"/>
-      <c r="BX20" s="225"/>
-      <c r="BY20" s="225"/>
-      <c r="BZ20" s="225"/>
-      <c r="CA20" s="225"/>
+      <c r="BV20" s="226"/>
+      <c r="BW20" s="226"/>
+      <c r="BX20" s="226"/>
+      <c r="BY20" s="226"/>
+      <c r="BZ20" s="226"/>
+      <c r="CA20" s="226"/>
     </row>
     <row r="21" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="AR21" s="225"/>
-      <c r="AS21" s="225"/>
-      <c r="AT21" s="225"/>
-      <c r="AU21" s="225"/>
+      <c r="AR21" s="226"/>
+      <c r="AS21" s="226"/>
+      <c r="AT21" s="226"/>
+      <c r="AU21" s="226"/>
       <c r="AV21" s="173"/>
       <c r="AW21" s="173"/>
       <c r="AX21" s="173"/>
@@ -9855,12 +9855,12 @@
       <c r="BS21" s="173"/>
       <c r="BT21" s="173"/>
       <c r="BU21" s="173"/>
-      <c r="BV21" s="225"/>
-      <c r="BW21" s="225"/>
-      <c r="BX21" s="225"/>
-      <c r="BY21" s="225"/>
-      <c r="BZ21" s="225"/>
-      <c r="CA21" s="225"/>
+      <c r="BV21" s="226"/>
+      <c r="BW21" s="226"/>
+      <c r="BX21" s="226"/>
+      <c r="BY21" s="226"/>
+      <c r="BZ21" s="226"/>
+      <c r="CA21" s="226"/>
     </row>
     <row r="22" spans="1:79" x14ac:dyDescent="0.25">
       <c r="A22" s="176"/>
@@ -10050,36 +10050,36 @@
       <c r="AU32" s="180"/>
       <c r="AV32" s="180"/>
       <c r="AW32" s="180"/>
-      <c r="AX32" s="225"/>
-      <c r="AY32" s="225"/>
-      <c r="AZ32" s="225"/>
-      <c r="BA32" s="225"/>
-      <c r="BB32" s="225"/>
-      <c r="BC32" s="225"/>
-      <c r="BD32" s="225"/>
-      <c r="BE32" s="225"/>
-      <c r="BF32" s="225"/>
-      <c r="BG32" s="225"/>
-      <c r="BH32" s="225"/>
-      <c r="BI32" s="225"/>
-      <c r="BJ32" s="225"/>
-      <c r="BK32" s="225"/>
-      <c r="BL32" s="225"/>
-      <c r="BM32" s="225"/>
-      <c r="BN32" s="225"/>
-      <c r="BO32" s="225"/>
-      <c r="BP32" s="225"/>
-      <c r="BQ32" s="225"/>
-      <c r="BR32" s="225"/>
-      <c r="BS32" s="225"/>
-      <c r="BT32" s="225"/>
-      <c r="BU32" s="225"/>
-      <c r="BV32" s="225"/>
-      <c r="BW32" s="225"/>
-      <c r="BX32" s="225"/>
-      <c r="BY32" s="225"/>
-      <c r="BZ32" s="225"/>
-      <c r="CA32" s="225"/>
+      <c r="AX32" s="226"/>
+      <c r="AY32" s="226"/>
+      <c r="AZ32" s="226"/>
+      <c r="BA32" s="226"/>
+      <c r="BB32" s="226"/>
+      <c r="BC32" s="226"/>
+      <c r="BD32" s="226"/>
+      <c r="BE32" s="226"/>
+      <c r="BF32" s="226"/>
+      <c r="BG32" s="226"/>
+      <c r="BH32" s="226"/>
+      <c r="BI32" s="226"/>
+      <c r="BJ32" s="226"/>
+      <c r="BK32" s="226"/>
+      <c r="BL32" s="226"/>
+      <c r="BM32" s="226"/>
+      <c r="BN32" s="226"/>
+      <c r="BO32" s="226"/>
+      <c r="BP32" s="226"/>
+      <c r="BQ32" s="226"/>
+      <c r="BR32" s="226"/>
+      <c r="BS32" s="226"/>
+      <c r="BT32" s="226"/>
+      <c r="BU32" s="226"/>
+      <c r="BV32" s="226"/>
+      <c r="BW32" s="226"/>
+      <c r="BX32" s="226"/>
+      <c r="BY32" s="226"/>
+      <c r="BZ32" s="226"/>
+      <c r="CA32" s="226"/>
     </row>
     <row r="33" spans="1:83" x14ac:dyDescent="0.25">
       <c r="AR33" s="180"/>
@@ -10088,54 +10088,54 @@
       <c r="AU33" s="180"/>
       <c r="AV33" s="180"/>
       <c r="AW33" s="180"/>
-      <c r="AX33" s="316" t="s">
+      <c r="AX33" s="317" t="s">
         <v>218</v>
       </c>
-      <c r="AY33" s="316"/>
-      <c r="AZ33" s="316" t="s">
+      <c r="AY33" s="317"/>
+      <c r="AZ33" s="317" t="s">
         <v>219</v>
       </c>
-      <c r="BA33" s="316"/>
-      <c r="BB33" s="316" t="s">
+      <c r="BA33" s="317"/>
+      <c r="BB33" s="317" t="s">
         <v>220</v>
       </c>
-      <c r="BC33" s="316"/>
+      <c r="BC33" s="317"/>
       <c r="BD33" s="184" t="s">
         <v>237</v>
       </c>
       <c r="BE33" s="184"/>
       <c r="BF33" s="184"/>
       <c r="BG33" s="184"/>
-      <c r="BH33" s="316" t="s">
+      <c r="BH33" s="317" t="s">
         <v>218</v>
       </c>
-      <c r="BI33" s="316"/>
-      <c r="BJ33" s="316" t="s">
+      <c r="BI33" s="317"/>
+      <c r="BJ33" s="317" t="s">
         <v>219</v>
       </c>
-      <c r="BK33" s="316"/>
-      <c r="BL33" s="316" t="s">
+      <c r="BK33" s="317"/>
+      <c r="BL33" s="317" t="s">
         <v>220</v>
       </c>
-      <c r="BM33" s="316"/>
+      <c r="BM33" s="317"/>
       <c r="BN33" s="184" t="s">
         <v>237</v>
       </c>
       <c r="BO33" s="184"/>
       <c r="BP33" s="184"/>
       <c r="BQ33" s="184"/>
-      <c r="BR33" s="316" t="s">
+      <c r="BR33" s="317" t="s">
         <v>218</v>
       </c>
-      <c r="BS33" s="316"/>
-      <c r="BT33" s="316" t="s">
+      <c r="BS33" s="317"/>
+      <c r="BT33" s="317" t="s">
         <v>219</v>
       </c>
-      <c r="BU33" s="316"/>
-      <c r="BV33" s="316" t="s">
+      <c r="BU33" s="317"/>
+      <c r="BV33" s="317" t="s">
         <v>220</v>
       </c>
-      <c r="BW33" s="316"/>
+      <c r="BW33" s="317"/>
       <c r="BX33" s="184" t="s">
         <v>237</v>
       </c>
@@ -10377,10 +10377,10 @@
       <c r="BG40" s="52"/>
       <c r="BH40" s="52"/>
       <c r="BI40" s="52"/>
-      <c r="BJ40" s="240"/>
-      <c r="BK40" s="240"/>
-      <c r="BL40" s="240"/>
-      <c r="BM40" s="240"/>
+      <c r="BJ40" s="201"/>
+      <c r="BK40" s="201"/>
+      <c r="BL40" s="201"/>
+      <c r="BM40" s="201"/>
       <c r="BN40" s="35" t="s">
         <v>224</v>
       </c>
@@ -10579,33 +10579,33 @@
       <c r="AN44" s="20"/>
       <c r="AO44" s="20"/>
       <c r="AP44" s="21"/>
-      <c r="AV44" s="317" t="s">
+      <c r="AV44" s="318" t="s">
         <v>225</v>
       </c>
-      <c r="AW44" s="317"/>
-      <c r="AX44" s="317"/>
-      <c r="AY44" s="317"/>
-      <c r="AZ44" s="317"/>
-      <c r="BA44" s="317"/>
-      <c r="BB44" s="317"/>
-      <c r="BC44" s="317" t="s">
+      <c r="AW44" s="318"/>
+      <c r="AX44" s="318"/>
+      <c r="AY44" s="318"/>
+      <c r="AZ44" s="318"/>
+      <c r="BA44" s="318"/>
+      <c r="BB44" s="318"/>
+      <c r="BC44" s="318" t="s">
         <v>228</v>
       </c>
-      <c r="BD44" s="317"/>
-      <c r="BE44" s="317"/>
-      <c r="BF44" s="317"/>
-      <c r="BG44" s="317"/>
-      <c r="BH44" s="317"/>
-      <c r="BI44" s="317"/>
-      <c r="BJ44" s="317" t="s">
+      <c r="BD44" s="318"/>
+      <c r="BE44" s="318"/>
+      <c r="BF44" s="318"/>
+      <c r="BG44" s="318"/>
+      <c r="BH44" s="318"/>
+      <c r="BI44" s="318"/>
+      <c r="BJ44" s="318" t="s">
         <v>231</v>
       </c>
-      <c r="BK44" s="317"/>
-      <c r="BL44" s="317"/>
-      <c r="BM44" s="317"/>
-      <c r="BN44" s="317"/>
-      <c r="BO44" s="317"/>
-      <c r="BP44" s="317"/>
+      <c r="BK44" s="318"/>
+      <c r="BL44" s="318"/>
+      <c r="BM44" s="318"/>
+      <c r="BN44" s="318"/>
+      <c r="BO44" s="318"/>
+      <c r="BP44" s="318"/>
     </row>
     <row r="45" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="176"/>
@@ -10626,33 +10626,33 @@
       <c r="AN45" s="186"/>
       <c r="AO45" s="186"/>
       <c r="AP45" s="187"/>
-      <c r="AV45" s="317" t="s">
+      <c r="AV45" s="318" t="s">
         <v>226</v>
       </c>
-      <c r="AW45" s="317"/>
-      <c r="AX45" s="317"/>
-      <c r="AY45" s="317"/>
-      <c r="AZ45" s="317"/>
-      <c r="BA45" s="317"/>
-      <c r="BB45" s="317"/>
-      <c r="BC45" s="317" t="s">
+      <c r="AW45" s="318"/>
+      <c r="AX45" s="318"/>
+      <c r="AY45" s="318"/>
+      <c r="AZ45" s="318"/>
+      <c r="BA45" s="318"/>
+      <c r="BB45" s="318"/>
+      <c r="BC45" s="318" t="s">
         <v>229</v>
       </c>
-      <c r="BD45" s="317"/>
-      <c r="BE45" s="317"/>
-      <c r="BF45" s="317"/>
-      <c r="BG45" s="317"/>
-      <c r="BH45" s="317"/>
-      <c r="BI45" s="317"/>
-      <c r="BJ45" s="317" t="s">
+      <c r="BD45" s="318"/>
+      <c r="BE45" s="318"/>
+      <c r="BF45" s="318"/>
+      <c r="BG45" s="318"/>
+      <c r="BH45" s="318"/>
+      <c r="BI45" s="318"/>
+      <c r="BJ45" s="318" t="s">
         <v>232</v>
       </c>
-      <c r="BK45" s="317"/>
-      <c r="BL45" s="317"/>
-      <c r="BM45" s="317"/>
-      <c r="BN45" s="317"/>
-      <c r="BO45" s="317"/>
-      <c r="BP45" s="317"/>
+      <c r="BK45" s="318"/>
+      <c r="BL45" s="318"/>
+      <c r="BM45" s="318"/>
+      <c r="BN45" s="318"/>
+      <c r="BO45" s="318"/>
+      <c r="BP45" s="318"/>
     </row>
     <row r="46" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AK46" s="31"/>
@@ -10661,33 +10661,33 @@
       <c r="AN46" s="189"/>
       <c r="AO46" s="189"/>
       <c r="AP46" s="190"/>
-      <c r="AV46" s="317" t="s">
+      <c r="AV46" s="318" t="s">
         <v>227</v>
       </c>
-      <c r="AW46" s="317"/>
-      <c r="AX46" s="317"/>
-      <c r="AY46" s="317"/>
-      <c r="AZ46" s="317"/>
-      <c r="BA46" s="317"/>
-      <c r="BB46" s="317"/>
-      <c r="BC46" s="317" t="s">
+      <c r="AW46" s="318"/>
+      <c r="AX46" s="318"/>
+      <c r="AY46" s="318"/>
+      <c r="AZ46" s="318"/>
+      <c r="BA46" s="318"/>
+      <c r="BB46" s="318"/>
+      <c r="BC46" s="318" t="s">
         <v>230</v>
       </c>
-      <c r="BD46" s="317"/>
-      <c r="BE46" s="317"/>
-      <c r="BF46" s="317"/>
-      <c r="BG46" s="317"/>
-      <c r="BH46" s="317"/>
-      <c r="BI46" s="317"/>
-      <c r="BJ46" s="317" t="s">
+      <c r="BD46" s="318"/>
+      <c r="BE46" s="318"/>
+      <c r="BF46" s="318"/>
+      <c r="BG46" s="318"/>
+      <c r="BH46" s="318"/>
+      <c r="BI46" s="318"/>
+      <c r="BJ46" s="318" t="s">
         <v>233</v>
       </c>
-      <c r="BK46" s="317"/>
-      <c r="BL46" s="317"/>
-      <c r="BM46" s="317"/>
-      <c r="BN46" s="317"/>
-      <c r="BO46" s="317"/>
-      <c r="BP46" s="317"/>
+      <c r="BK46" s="318"/>
+      <c r="BL46" s="318"/>
+      <c r="BM46" s="318"/>
+      <c r="BN46" s="318"/>
+      <c r="BO46" s="318"/>
+      <c r="BP46" s="318"/>
     </row>
     <row r="47" spans="1:83" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
@@ -11834,10 +11834,10 @@
       <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="321"/>
-      <c r="B3" s="321"/>
-      <c r="C3" s="321"/>
-      <c r="D3" s="321"/>
+      <c r="A3" s="322"/>
+      <c r="B3" s="322"/>
+      <c r="C3" s="322"/>
+      <c r="D3" s="322"/>
       <c r="E3" s="74"/>
       <c r="G3" s="75"/>
       <c r="H3" s="58" t="s">
@@ -11855,18 +11855,18 @@
       </c>
       <c r="B4" s="196"/>
       <c r="C4" s="197"/>
-      <c r="D4" s="318"/>
-      <c r="E4" s="322"/>
-      <c r="F4" s="318"/>
-      <c r="G4" s="322"/>
-      <c r="H4" s="318"/>
-      <c r="I4" s="322"/>
-      <c r="J4" s="318"/>
-      <c r="K4" s="322"/>
-      <c r="L4" s="318"/>
-      <c r="M4" s="322"/>
-      <c r="N4" s="318"/>
-      <c r="O4" s="322"/>
+      <c r="D4" s="319"/>
+      <c r="E4" s="323"/>
+      <c r="F4" s="319"/>
+      <c r="G4" s="323"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="323"/>
+      <c r="J4" s="319"/>
+      <c r="K4" s="323"/>
+      <c r="L4" s="319"/>
+      <c r="M4" s="323"/>
+      <c r="N4" s="319"/>
+      <c r="O4" s="323"/>
     </row>
     <row r="5" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="185" t="s">
@@ -11874,73 +11874,73 @@
       </c>
       <c r="B5" s="186"/>
       <c r="C5" s="187"/>
-      <c r="D5" s="319"/>
-      <c r="E5" s="320"/>
-      <c r="F5" s="319"/>
-      <c r="G5" s="320"/>
-      <c r="H5" s="319"/>
-      <c r="I5" s="320"/>
-      <c r="J5" s="319"/>
-      <c r="K5" s="320"/>
-      <c r="L5" s="319"/>
-      <c r="M5" s="320"/>
-      <c r="N5" s="319"/>
-      <c r="O5" s="320"/>
+      <c r="D5" s="320"/>
+      <c r="E5" s="321"/>
+      <c r="F5" s="320"/>
+      <c r="G5" s="321"/>
+      <c r="H5" s="320"/>
+      <c r="I5" s="321"/>
+      <c r="J5" s="320"/>
+      <c r="K5" s="321"/>
+      <c r="L5" s="320"/>
+      <c r="M5" s="321"/>
+      <c r="N5" s="320"/>
+      <c r="O5" s="321"/>
     </row>
     <row r="6" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="323" t="s">
+      <c r="A6" s="324" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="324"/>
-      <c r="C6" s="325"/>
-      <c r="D6" s="323"/>
-      <c r="E6" s="325"/>
-      <c r="F6" s="323"/>
-      <c r="G6" s="325"/>
-      <c r="H6" s="323"/>
-      <c r="I6" s="325"/>
-      <c r="J6" s="323"/>
-      <c r="K6" s="325"/>
-      <c r="L6" s="323"/>
-      <c r="M6" s="325"/>
-      <c r="N6" s="323"/>
-      <c r="O6" s="325"/>
+      <c r="B6" s="325"/>
+      <c r="C6" s="326"/>
+      <c r="D6" s="324"/>
+      <c r="E6" s="326"/>
+      <c r="F6" s="324"/>
+      <c r="G6" s="326"/>
+      <c r="H6" s="324"/>
+      <c r="I6" s="326"/>
+      <c r="J6" s="324"/>
+      <c r="K6" s="326"/>
+      <c r="L6" s="324"/>
+      <c r="M6" s="326"/>
+      <c r="N6" s="324"/>
+      <c r="O6" s="326"/>
     </row>
     <row r="7" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="326"/>
-      <c r="B7" s="327"/>
-      <c r="C7" s="328"/>
-      <c r="D7" s="326"/>
-      <c r="E7" s="328"/>
-      <c r="F7" s="326"/>
-      <c r="G7" s="328"/>
-      <c r="H7" s="326"/>
-      <c r="I7" s="328"/>
-      <c r="J7" s="326"/>
-      <c r="K7" s="328"/>
-      <c r="L7" s="326"/>
-      <c r="M7" s="328"/>
-      <c r="N7" s="326"/>
-      <c r="O7" s="328"/>
+      <c r="A7" s="327"/>
+      <c r="B7" s="328"/>
+      <c r="C7" s="329"/>
+      <c r="D7" s="327"/>
+      <c r="E7" s="329"/>
+      <c r="F7" s="327"/>
+      <c r="G7" s="329"/>
+      <c r="H7" s="327"/>
+      <c r="I7" s="329"/>
+      <c r="J7" s="327"/>
+      <c r="K7" s="329"/>
+      <c r="L7" s="327"/>
+      <c r="M7" s="329"/>
+      <c r="N7" s="327"/>
+      <c r="O7" s="329"/>
     </row>
     <row r="8" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="329" t="s">
+      <c r="A8" s="330" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="331"/>
-      <c r="C8" s="330"/>
-      <c r="D8" s="329"/>
-      <c r="E8" s="330"/>
-      <c r="F8" s="329"/>
-      <c r="G8" s="330"/>
-      <c r="H8" s="329"/>
-      <c r="I8" s="330"/>
-      <c r="J8" s="329"/>
-      <c r="K8" s="330"/>
-      <c r="L8" s="329"/>
-      <c r="M8" s="330"/>
-      <c r="N8" s="329"/>
-      <c r="O8" s="330"/>
+      <c r="B8" s="332"/>
+      <c r="C8" s="331"/>
+      <c r="D8" s="330"/>
+      <c r="E8" s="331"/>
+      <c r="F8" s="330"/>
+      <c r="G8" s="331"/>
+      <c r="H8" s="330"/>
+      <c r="I8" s="331"/>
+      <c r="J8" s="330"/>
+      <c r="K8" s="331"/>
+      <c r="L8" s="330"/>
+      <c r="M8" s="331"/>
+      <c r="N8" s="330"/>
+      <c r="O8" s="331"/>
     </row>
     <row r="9" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="195" t="s">
@@ -11948,73 +11948,73 @@
       </c>
       <c r="B9" s="196"/>
       <c r="C9" s="197"/>
-      <c r="D9" s="319"/>
-      <c r="E9" s="320"/>
-      <c r="F9" s="319"/>
-      <c r="G9" s="320"/>
-      <c r="H9" s="319"/>
-      <c r="I9" s="320"/>
-      <c r="J9" s="319"/>
-      <c r="K9" s="320"/>
-      <c r="L9" s="319"/>
-      <c r="M9" s="320"/>
-      <c r="N9" s="319"/>
-      <c r="O9" s="320"/>
+      <c r="D9" s="320"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="320"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="320"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="320"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="320"/>
+      <c r="M9" s="321"/>
+      <c r="N9" s="320"/>
+      <c r="O9" s="321"/>
     </row>
     <row r="10" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="323" t="s">
+      <c r="A10" s="324" t="s">
         <v>258</v>
       </c>
-      <c r="B10" s="324"/>
-      <c r="C10" s="325"/>
-      <c r="D10" s="323"/>
-      <c r="E10" s="325"/>
-      <c r="F10" s="323"/>
-      <c r="G10" s="325"/>
-      <c r="H10" s="323"/>
-      <c r="I10" s="325"/>
-      <c r="J10" s="323"/>
-      <c r="K10" s="325"/>
-      <c r="L10" s="323"/>
-      <c r="M10" s="325"/>
-      <c r="N10" s="323"/>
-      <c r="O10" s="325"/>
+      <c r="B10" s="325"/>
+      <c r="C10" s="326"/>
+      <c r="D10" s="324"/>
+      <c r="E10" s="326"/>
+      <c r="F10" s="324"/>
+      <c r="G10" s="326"/>
+      <c r="H10" s="324"/>
+      <c r="I10" s="326"/>
+      <c r="J10" s="324"/>
+      <c r="K10" s="326"/>
+      <c r="L10" s="324"/>
+      <c r="M10" s="326"/>
+      <c r="N10" s="324"/>
+      <c r="O10" s="326"/>
     </row>
     <row r="11" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="326"/>
-      <c r="B11" s="327"/>
-      <c r="C11" s="328"/>
-      <c r="D11" s="326"/>
-      <c r="E11" s="328"/>
-      <c r="F11" s="326"/>
-      <c r="G11" s="328"/>
-      <c r="H11" s="326"/>
-      <c r="I11" s="328"/>
-      <c r="J11" s="326"/>
-      <c r="K11" s="328"/>
-      <c r="L11" s="326"/>
-      <c r="M11" s="328"/>
-      <c r="N11" s="326"/>
-      <c r="O11" s="328"/>
+      <c r="A11" s="327"/>
+      <c r="B11" s="328"/>
+      <c r="C11" s="329"/>
+      <c r="D11" s="327"/>
+      <c r="E11" s="329"/>
+      <c r="F11" s="327"/>
+      <c r="G11" s="329"/>
+      <c r="H11" s="327"/>
+      <c r="I11" s="329"/>
+      <c r="J11" s="327"/>
+      <c r="K11" s="329"/>
+      <c r="L11" s="327"/>
+      <c r="M11" s="329"/>
+      <c r="N11" s="327"/>
+      <c r="O11" s="329"/>
     </row>
     <row r="12" spans="1:15" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="329" t="s">
+      <c r="A12" s="330" t="s">
         <v>259</v>
       </c>
-      <c r="B12" s="331"/>
-      <c r="C12" s="330"/>
-      <c r="D12" s="329"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="329"/>
-      <c r="G12" s="330"/>
-      <c r="H12" s="329"/>
-      <c r="I12" s="330"/>
-      <c r="J12" s="329"/>
-      <c r="K12" s="330"/>
-      <c r="L12" s="329"/>
-      <c r="M12" s="330"/>
-      <c r="N12" s="329"/>
-      <c r="O12" s="330"/>
+      <c r="B12" s="332"/>
+      <c r="C12" s="331"/>
+      <c r="D12" s="330"/>
+      <c r="E12" s="331"/>
+      <c r="F12" s="330"/>
+      <c r="G12" s="331"/>
+      <c r="H12" s="330"/>
+      <c r="I12" s="331"/>
+      <c r="J12" s="330"/>
+      <c r="K12" s="331"/>
+      <c r="L12" s="330"/>
+      <c r="M12" s="331"/>
+      <c r="N12" s="330"/>
+      <c r="O12" s="331"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="72" t="s">
@@ -12345,7 +12345,7 @@
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="332" t="s">
+      <c r="A5" s="333" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="154"/>
@@ -13000,8 +13000,8 @@
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
-      <c r="M2" s="345"/>
-      <c r="N2" s="345"/>
+      <c r="M2" s="346"/>
+      <c r="N2" s="346"/>
       <c r="O2"/>
       <c r="P2"/>
       <c r="Q2"/>
@@ -13010,8 +13010,8 @@
       <c r="A3" s="161" t="s">
         <v>281</v>
       </c>
-      <c r="B3" s="343"/>
-      <c r="C3" s="344"/>
+      <c r="B3" s="344"/>
+      <c r="C3" s="345"/>
       <c r="D3" s="132"/>
       <c r="E3" s="134"/>
       <c r="F3" s="132"/>
@@ -13029,37 +13029,37 @@
       <c r="A4" s="129" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="346"/>
-      <c r="C4" s="347"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="339"/>
-      <c r="F4" s="338"/>
-      <c r="G4" s="339"/>
-      <c r="H4" s="338"/>
-      <c r="I4" s="339"/>
-      <c r="J4" s="338"/>
-      <c r="K4" s="339"/>
-      <c r="L4" s="338"/>
-      <c r="M4" s="339"/>
-      <c r="N4" s="338"/>
-      <c r="O4" s="339"/>
+      <c r="B4" s="347"/>
+      <c r="C4" s="348"/>
+      <c r="D4" s="339"/>
+      <c r="E4" s="340"/>
+      <c r="F4" s="339"/>
+      <c r="G4" s="340"/>
+      <c r="H4" s="339"/>
+      <c r="I4" s="340"/>
+      <c r="J4" s="339"/>
+      <c r="K4" s="340"/>
+      <c r="L4" s="339"/>
+      <c r="M4" s="340"/>
+      <c r="N4" s="339"/>
+      <c r="O4" s="340"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="342"/>
-      <c r="B5" s="348"/>
-      <c r="C5" s="349"/>
-      <c r="D5" s="340"/>
-      <c r="E5" s="341"/>
-      <c r="F5" s="340"/>
-      <c r="G5" s="341"/>
-      <c r="H5" s="340"/>
-      <c r="I5" s="341"/>
-      <c r="J5" s="340"/>
-      <c r="K5" s="341"/>
-      <c r="L5" s="340"/>
-      <c r="M5" s="341"/>
-      <c r="N5" s="340"/>
-      <c r="O5" s="341"/>
+      <c r="A5" s="343"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="350"/>
+      <c r="D5" s="341"/>
+      <c r="E5" s="342"/>
+      <c r="F5" s="341"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="341"/>
+      <c r="I5" s="342"/>
+      <c r="J5" s="341"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="341"/>
+      <c r="M5" s="342"/>
+      <c r="N5" s="341"/>
+      <c r="O5" s="342"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="162" t="s">
@@ -13067,35 +13067,35 @@
       </c>
       <c r="B6" s="136"/>
       <c r="C6" s="137"/>
-      <c r="D6" s="338"/>
-      <c r="E6" s="339"/>
-      <c r="F6" s="338"/>
-      <c r="G6" s="339"/>
-      <c r="H6" s="338"/>
-      <c r="I6" s="339"/>
-      <c r="J6" s="338"/>
-      <c r="K6" s="339"/>
-      <c r="L6" s="338"/>
-      <c r="M6" s="339"/>
-      <c r="N6" s="338"/>
-      <c r="O6" s="339"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="340"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="340"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="340"/>
+      <c r="J6" s="339"/>
+      <c r="K6" s="340"/>
+      <c r="L6" s="339"/>
+      <c r="M6" s="340"/>
+      <c r="N6" s="339"/>
+      <c r="O6" s="340"/>
     </row>
     <row r="7" spans="1:17" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="138"/>
       <c r="B7" s="139"/>
       <c r="C7" s="140"/>
-      <c r="D7" s="340"/>
-      <c r="E7" s="341"/>
-      <c r="F7" s="340"/>
-      <c r="G7" s="341"/>
-      <c r="H7" s="340"/>
-      <c r="I7" s="341"/>
-      <c r="J7" s="340"/>
-      <c r="K7" s="341"/>
-      <c r="L7" s="340"/>
-      <c r="M7" s="341"/>
-      <c r="N7" s="340"/>
-      <c r="O7" s="341"/>
+      <c r="D7" s="341"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="341"/>
+      <c r="G7" s="342"/>
+      <c r="H7" s="341"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="341"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="341"/>
+      <c r="M7" s="342"/>
+      <c r="N7" s="341"/>
+      <c r="O7" s="342"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="129" t="s">
@@ -13193,11 +13193,11 @@
       <c r="O12" s="160"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="342" t="s">
+      <c r="A13" s="343" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="343"/>
-      <c r="C13" s="344"/>
+      <c r="B13" s="344"/>
+      <c r="C13" s="345"/>
       <c r="D13" s="158"/>
       <c r="E13" s="160"/>
       <c r="F13" s="158"/>
@@ -13231,40 +13231,40 @@
       <c r="O14"/>
     </row>
     <row r="16" spans="1:17" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="337" t="s">
+      <c r="A16" s="338" t="s">
         <v>276</v>
       </c>
-      <c r="B16" s="337"/>
-      <c r="C16" s="337"/>
-      <c r="D16" s="337"/>
-      <c r="E16" s="337"/>
-      <c r="F16" s="337"/>
-      <c r="G16" s="337"/>
-      <c r="H16" s="337"/>
-      <c r="I16" s="337"/>
-      <c r="J16" s="337"/>
-      <c r="K16" s="337"/>
-      <c r="L16" s="337"/>
-      <c r="M16" s="337"/>
-      <c r="N16" s="337"/>
-      <c r="O16" s="337"/>
+      <c r="B16" s="338"/>
+      <c r="C16" s="338"/>
+      <c r="D16" s="338"/>
+      <c r="E16" s="338"/>
+      <c r="F16" s="338"/>
+      <c r="G16" s="338"/>
+      <c r="H16" s="338"/>
+      <c r="I16" s="338"/>
+      <c r="J16" s="338"/>
+      <c r="K16" s="338"/>
+      <c r="L16" s="338"/>
+      <c r="M16" s="338"/>
+      <c r="N16" s="338"/>
+      <c r="O16" s="338"/>
     </row>
     <row r="17" spans="1:15" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="337"/>
-      <c r="B17" s="337"/>
-      <c r="C17" s="337"/>
-      <c r="D17" s="337"/>
-      <c r="E17" s="337"/>
-      <c r="F17" s="337"/>
-      <c r="G17" s="337"/>
-      <c r="H17" s="337"/>
-      <c r="I17" s="337"/>
-      <c r="J17" s="337"/>
-      <c r="K17" s="337"/>
-      <c r="L17" s="337"/>
-      <c r="M17" s="337"/>
-      <c r="N17" s="337"/>
-      <c r="O17" s="337"/>
+      <c r="A17" s="338"/>
+      <c r="B17" s="338"/>
+      <c r="C17" s="338"/>
+      <c r="D17" s="338"/>
+      <c r="E17" s="338"/>
+      <c r="F17" s="338"/>
+      <c r="G17" s="338"/>
+      <c r="H17" s="338"/>
+      <c r="I17" s="338"/>
+      <c r="J17" s="338"/>
+      <c r="K17" s="338"/>
+      <c r="L17" s="338"/>
+      <c r="M17" s="338"/>
+      <c r="N17" s="338"/>
+      <c r="O17" s="338"/>
     </row>
     <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A18" s="83" t="s">
@@ -13279,40 +13279,40 @@
       <c r="J19" s="85"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="336" t="s">
+      <c r="A20" s="337" t="s">
         <v>278</v>
       </c>
-      <c r="B20" s="336"/>
-      <c r="C20" s="336"/>
-      <c r="D20" s="336"/>
-      <c r="E20" s="336"/>
-      <c r="F20" s="336"/>
-      <c r="G20" s="336"/>
-      <c r="H20" s="336"/>
-      <c r="I20" s="336"/>
-      <c r="J20" s="336"/>
-      <c r="K20" s="336"/>
-      <c r="L20" s="336"/>
-      <c r="M20" s="336"/>
-      <c r="N20" s="336"/>
-      <c r="O20" s="336"/>
+      <c r="B20" s="337"/>
+      <c r="C20" s="337"/>
+      <c r="D20" s="337"/>
+      <c r="E20" s="337"/>
+      <c r="F20" s="337"/>
+      <c r="G20" s="337"/>
+      <c r="H20" s="337"/>
+      <c r="I20" s="337"/>
+      <c r="J20" s="337"/>
+      <c r="K20" s="337"/>
+      <c r="L20" s="337"/>
+      <c r="M20" s="337"/>
+      <c r="N20" s="337"/>
+      <c r="O20" s="337"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="336"/>
-      <c r="B21" s="336"/>
-      <c r="C21" s="336"/>
-      <c r="D21" s="336"/>
-      <c r="E21" s="336"/>
-      <c r="F21" s="336"/>
-      <c r="G21" s="336"/>
-      <c r="H21" s="336"/>
-      <c r="I21" s="336"/>
-      <c r="J21" s="336"/>
-      <c r="K21" s="336"/>
-      <c r="L21" s="336"/>
-      <c r="M21" s="336"/>
-      <c r="N21" s="336"/>
-      <c r="O21" s="336"/>
+      <c r="A21" s="337"/>
+      <c r="B21" s="337"/>
+      <c r="C21" s="337"/>
+      <c r="D21" s="337"/>
+      <c r="E21" s="337"/>
+      <c r="F21" s="337"/>
+      <c r="G21" s="337"/>
+      <c r="H21" s="337"/>
+      <c r="I21" s="337"/>
+      <c r="J21" s="337"/>
+      <c r="K21" s="337"/>
+      <c r="L21" s="337"/>
+      <c r="M21" s="337"/>
+      <c r="N21" s="337"/>
+      <c r="O21" s="337"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="84"/>
@@ -13332,30 +13332,30 @@
       <c r="O22" s="84"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="333" t="s">
+      <c r="A23" s="334" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="334"/>
-      <c r="C23" s="335"/>
-      <c r="D23" s="318"/>
-      <c r="E23" s="322"/>
-      <c r="F23" s="318"/>
-      <c r="G23" s="322"/>
-      <c r="H23" s="318"/>
-      <c r="I23" s="322"/>
-      <c r="J23" s="318"/>
-      <c r="K23" s="322"/>
-      <c r="L23" s="318"/>
-      <c r="M23" s="322"/>
-      <c r="N23" s="318"/>
-      <c r="O23" s="322"/>
+      <c r="B23" s="335"/>
+      <c r="C23" s="336"/>
+      <c r="D23" s="319"/>
+      <c r="E23" s="323"/>
+      <c r="F23" s="319"/>
+      <c r="G23" s="323"/>
+      <c r="H23" s="319"/>
+      <c r="I23" s="323"/>
+      <c r="J23" s="319"/>
+      <c r="K23" s="323"/>
+      <c r="L23" s="319"/>
+      <c r="M23" s="323"/>
+      <c r="N23" s="319"/>
+      <c r="O23" s="323"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="333" t="s">
+      <c r="A24" s="334" t="s">
         <v>274</v>
       </c>
-      <c r="B24" s="334"/>
-      <c r="C24" s="335"/>
+      <c r="B24" s="335"/>
+      <c r="C24" s="336"/>
       <c r="D24" s="195"/>
       <c r="E24" s="197"/>
       <c r="F24" s="195"/>
@@ -13370,11 +13370,11 @@
       <c r="O24" s="197"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="333" t="s">
+      <c r="A25" s="334" t="s">
         <v>273</v>
       </c>
-      <c r="B25" s="334"/>
-      <c r="C25" s="335"/>
+      <c r="B25" s="335"/>
+      <c r="C25" s="336"/>
       <c r="D25" s="195"/>
       <c r="E25" s="197"/>
       <c r="F25" s="195"/>
@@ -22832,17 +22832,17 @@
       <c r="BF30" s="35"/>
       <c r="BG30" s="35"/>
       <c r="BH30" s="35"/>
-      <c r="BI30" s="240"/>
-      <c r="BJ30" s="240"/>
-      <c r="BK30" s="240"/>
-      <c r="BL30" s="240"/>
-      <c r="BM30" s="240"/>
-      <c r="BN30" s="240"/>
+      <c r="BI30" s="201"/>
+      <c r="BJ30" s="201"/>
+      <c r="BK30" s="201"/>
+      <c r="BL30" s="201"/>
+      <c r="BM30" s="201"/>
+      <c r="BN30" s="201"/>
       <c r="BO30" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="BP30" s="240"/>
-      <c r="BQ30" s="240"/>
+      <c r="BP30" s="201"/>
+      <c r="BQ30" s="201"/>
       <c r="BR30" s="171"/>
       <c r="BS30" s="171"/>
       <c r="BT30" s="35"/>
@@ -25568,37 +25568,37 @@
       <c r="AO19" s="51"/>
       <c r="AP19" s="51"/>
       <c r="AQ19" s="51"/>
-      <c r="AR19" s="201">
+      <c r="AR19" s="202">
         <v>7</v>
       </c>
-      <c r="AS19" s="202"/>
-      <c r="AT19" s="207" t="s">
+      <c r="AS19" s="203"/>
+      <c r="AT19" s="208" t="s">
         <v>140</v>
       </c>
-      <c r="AU19" s="208"/>
-      <c r="AV19" s="208"/>
-      <c r="AW19" s="208"/>
-      <c r="AX19" s="208"/>
-      <c r="AY19" s="208"/>
-      <c r="AZ19" s="208"/>
-      <c r="BA19" s="208"/>
-      <c r="BB19" s="208"/>
-      <c r="BC19" s="208"/>
-      <c r="BD19" s="208"/>
-      <c r="BE19" s="208"/>
-      <c r="BF19" s="208"/>
-      <c r="BG19" s="208"/>
-      <c r="BH19" s="209"/>
-      <c r="BI19" s="216" t="s">
+      <c r="AU19" s="209"/>
+      <c r="AV19" s="209"/>
+      <c r="AW19" s="209"/>
+      <c r="AX19" s="209"/>
+      <c r="AY19" s="209"/>
+      <c r="AZ19" s="209"/>
+      <c r="BA19" s="209"/>
+      <c r="BB19" s="209"/>
+      <c r="BC19" s="209"/>
+      <c r="BD19" s="209"/>
+      <c r="BE19" s="209"/>
+      <c r="BF19" s="209"/>
+      <c r="BG19" s="209"/>
+      <c r="BH19" s="210"/>
+      <c r="BI19" s="217" t="s">
         <v>134</v>
       </c>
-      <c r="BJ19" s="217"/>
-      <c r="BK19" s="217"/>
-      <c r="BL19" s="217"/>
-      <c r="BM19" s="217"/>
-      <c r="BN19" s="217"/>
-      <c r="BO19" s="217"/>
-      <c r="BP19" s="218"/>
+      <c r="BJ19" s="218"/>
+      <c r="BK19" s="218"/>
+      <c r="BL19" s="218"/>
+      <c r="BM19" s="218"/>
+      <c r="BN19" s="218"/>
+      <c r="BO19" s="218"/>
+      <c r="BP19" s="219"/>
       <c r="BQ19" s="185"/>
       <c r="BR19" s="186"/>
       <c r="BS19" s="186"/>
@@ -25655,31 +25655,31 @@
       <c r="AO20" s="51"/>
       <c r="AP20" s="51"/>
       <c r="AQ20" s="51"/>
-      <c r="AR20" s="203"/>
-      <c r="AS20" s="204"/>
-      <c r="AT20" s="210"/>
-      <c r="AU20" s="211"/>
-      <c r="AV20" s="211"/>
-      <c r="AW20" s="211"/>
-      <c r="AX20" s="211"/>
-      <c r="AY20" s="211"/>
-      <c r="AZ20" s="211"/>
-      <c r="BA20" s="211"/>
-      <c r="BB20" s="211"/>
-      <c r="BC20" s="211"/>
-      <c r="BD20" s="211"/>
-      <c r="BE20" s="211"/>
-      <c r="BF20" s="211"/>
-      <c r="BG20" s="211"/>
-      <c r="BH20" s="212"/>
-      <c r="BI20" s="219"/>
-      <c r="BJ20" s="220"/>
-      <c r="BK20" s="220"/>
-      <c r="BL20" s="220"/>
-      <c r="BM20" s="220"/>
-      <c r="BN20" s="220"/>
-      <c r="BO20" s="220"/>
-      <c r="BP20" s="221"/>
+      <c r="AR20" s="204"/>
+      <c r="AS20" s="205"/>
+      <c r="AT20" s="211"/>
+      <c r="AU20" s="212"/>
+      <c r="AV20" s="212"/>
+      <c r="AW20" s="212"/>
+      <c r="AX20" s="212"/>
+      <c r="AY20" s="212"/>
+      <c r="AZ20" s="212"/>
+      <c r="BA20" s="212"/>
+      <c r="BB20" s="212"/>
+      <c r="BC20" s="212"/>
+      <c r="BD20" s="212"/>
+      <c r="BE20" s="212"/>
+      <c r="BF20" s="212"/>
+      <c r="BG20" s="212"/>
+      <c r="BH20" s="213"/>
+      <c r="BI20" s="220"/>
+      <c r="BJ20" s="221"/>
+      <c r="BK20" s="221"/>
+      <c r="BL20" s="221"/>
+      <c r="BM20" s="221"/>
+      <c r="BN20" s="221"/>
+      <c r="BO20" s="221"/>
+      <c r="BP20" s="222"/>
       <c r="BQ20" s="188"/>
       <c r="BR20" s="189"/>
       <c r="BS20" s="189"/>
@@ -25736,31 +25736,31 @@
       <c r="AO21" s="51"/>
       <c r="AP21" s="51"/>
       <c r="AQ21" s="51"/>
-      <c r="AR21" s="205"/>
-      <c r="AS21" s="206"/>
-      <c r="AT21" s="213"/>
-      <c r="AU21" s="214"/>
-      <c r="AV21" s="214"/>
-      <c r="AW21" s="214"/>
-      <c r="AX21" s="214"/>
-      <c r="AY21" s="214"/>
-      <c r="AZ21" s="214"/>
-      <c r="BA21" s="214"/>
-      <c r="BB21" s="214"/>
-      <c r="BC21" s="214"/>
-      <c r="BD21" s="214"/>
-      <c r="BE21" s="214"/>
-      <c r="BF21" s="214"/>
-      <c r="BG21" s="214"/>
-      <c r="BH21" s="215"/>
-      <c r="BI21" s="222"/>
-      <c r="BJ21" s="223"/>
-      <c r="BK21" s="223"/>
-      <c r="BL21" s="223"/>
-      <c r="BM21" s="223"/>
-      <c r="BN21" s="223"/>
-      <c r="BO21" s="223"/>
-      <c r="BP21" s="224"/>
+      <c r="AR21" s="206"/>
+      <c r="AS21" s="207"/>
+      <c r="AT21" s="214"/>
+      <c r="AU21" s="215"/>
+      <c r="AV21" s="215"/>
+      <c r="AW21" s="215"/>
+      <c r="AX21" s="215"/>
+      <c r="AY21" s="215"/>
+      <c r="AZ21" s="215"/>
+      <c r="BA21" s="215"/>
+      <c r="BB21" s="215"/>
+      <c r="BC21" s="215"/>
+      <c r="BD21" s="215"/>
+      <c r="BE21" s="215"/>
+      <c r="BF21" s="215"/>
+      <c r="BG21" s="215"/>
+      <c r="BH21" s="216"/>
+      <c r="BI21" s="223"/>
+      <c r="BJ21" s="224"/>
+      <c r="BK21" s="224"/>
+      <c r="BL21" s="224"/>
+      <c r="BM21" s="224"/>
+      <c r="BN21" s="224"/>
+      <c r="BO21" s="224"/>
+      <c r="BP21" s="225"/>
       <c r="BQ21" s="191"/>
       <c r="BR21" s="192"/>
       <c r="BS21" s="192"/>
@@ -25937,17 +25937,17 @@
       <c r="BD27" s="35"/>
       <c r="BE27" s="171"/>
       <c r="BF27" s="171"/>
-      <c r="BG27" s="240"/>
-      <c r="BH27" s="240"/>
-      <c r="BI27" s="240"/>
-      <c r="BJ27" s="240"/>
+      <c r="BG27" s="201"/>
+      <c r="BH27" s="201"/>
+      <c r="BI27" s="201"/>
+      <c r="BJ27" s="201"/>
       <c r="BK27" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="BL27" s="240"/>
-      <c r="BM27" s="240"/>
-      <c r="BN27" s="240"/>
-      <c r="BO27" s="240"/>
+      <c r="BL27" s="201"/>
+      <c r="BM27" s="201"/>
+      <c r="BN27" s="201"/>
+      <c r="BO27" s="201"/>
       <c r="BT27" s="35"/>
       <c r="BU27" s="35"/>
     </row>
@@ -27453,9 +27453,9 @@
       <c r="AR2" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="BP2" s="226"/>
-      <c r="BQ2" s="226"/>
-      <c r="BR2" s="226"/>
+      <c r="BP2" s="227"/>
+      <c r="BQ2" s="227"/>
+      <c r="BR2" s="227"/>
       <c r="BS2" s="13" t="s">
         <v>291</v>
       </c>
@@ -27494,30 +27494,30 @@
       <c r="BA4" s="241"/>
       <c r="BB4" s="241"/>
       <c r="BC4" s="241"/>
-      <c r="BD4" s="225"/>
-      <c r="BE4" s="225"/>
-      <c r="BF4" s="225"/>
-      <c r="BG4" s="225"/>
-      <c r="BH4" s="225"/>
-      <c r="BI4" s="225"/>
-      <c r="BJ4" s="225"/>
-      <c r="BK4" s="225"/>
-      <c r="BL4" s="225"/>
-      <c r="BM4" s="225"/>
-      <c r="BN4" s="225"/>
-      <c r="BO4" s="225"/>
-      <c r="BP4" s="225"/>
-      <c r="BQ4" s="225"/>
-      <c r="BR4" s="225"/>
-      <c r="BS4" s="225"/>
-      <c r="BT4" s="225"/>
-      <c r="BU4" s="225"/>
-      <c r="BV4" s="225"/>
-      <c r="BW4" s="225"/>
-      <c r="BX4" s="225"/>
-      <c r="BY4" s="225"/>
-      <c r="BZ4" s="225"/>
-      <c r="CA4" s="225"/>
+      <c r="BD4" s="226"/>
+      <c r="BE4" s="226"/>
+      <c r="BF4" s="226"/>
+      <c r="BG4" s="226"/>
+      <c r="BH4" s="226"/>
+      <c r="BI4" s="226"/>
+      <c r="BJ4" s="226"/>
+      <c r="BK4" s="226"/>
+      <c r="BL4" s="226"/>
+      <c r="BM4" s="226"/>
+      <c r="BN4" s="226"/>
+      <c r="BO4" s="226"/>
+      <c r="BP4" s="226"/>
+      <c r="BQ4" s="226"/>
+      <c r="BR4" s="226"/>
+      <c r="BS4" s="226"/>
+      <c r="BT4" s="226"/>
+      <c r="BU4" s="226"/>
+      <c r="BV4" s="226"/>
+      <c r="BW4" s="226"/>
+      <c r="BX4" s="226"/>
+      <c r="BY4" s="226"/>
+      <c r="BZ4" s="226"/>
+      <c r="CA4" s="226"/>
       <c r="CB4" s="58"/>
     </row>
     <row r="5" spans="1:80" x14ac:dyDescent="0.25">
@@ -27624,11 +27624,11 @@
       <c r="BA6" s="173"/>
       <c r="BB6" s="173"/>
       <c r="BC6" s="173"/>
-      <c r="BD6" s="225"/>
-      <c r="BE6" s="225"/>
-      <c r="BF6" s="225"/>
-      <c r="BG6" s="225"/>
-      <c r="BH6" s="225"/>
+      <c r="BD6" s="226"/>
+      <c r="BE6" s="226"/>
+      <c r="BF6" s="226"/>
+      <c r="BG6" s="226"/>
+      <c r="BH6" s="226"/>
       <c r="BI6" s="173"/>
       <c r="BJ6" s="173"/>
       <c r="BK6" s="173"/>
@@ -27636,11 +27636,11 @@
       <c r="BM6" s="173"/>
       <c r="BN6" s="173"/>
       <c r="BO6" s="173"/>
-      <c r="BP6" s="225"/>
-      <c r="BQ6" s="225"/>
-      <c r="BR6" s="225"/>
-      <c r="BS6" s="225"/>
-      <c r="BT6" s="225"/>
+      <c r="BP6" s="226"/>
+      <c r="BQ6" s="226"/>
+      <c r="BR6" s="226"/>
+      <c r="BS6" s="226"/>
+      <c r="BT6" s="226"/>
       <c r="BU6" s="173"/>
       <c r="BV6" s="173"/>
       <c r="BW6" s="173"/>
@@ -27669,11 +27669,11 @@
       <c r="BA7" s="173"/>
       <c r="BB7" s="173"/>
       <c r="BC7" s="173"/>
-      <c r="BD7" s="225"/>
-      <c r="BE7" s="225"/>
-      <c r="BF7" s="225"/>
-      <c r="BG7" s="225"/>
-      <c r="BH7" s="225"/>
+      <c r="BD7" s="226"/>
+      <c r="BE7" s="226"/>
+      <c r="BF7" s="226"/>
+      <c r="BG7" s="226"/>
+      <c r="BH7" s="226"/>
       <c r="BI7" s="173"/>
       <c r="BJ7" s="173"/>
       <c r="BK7" s="173"/>
@@ -27681,11 +27681,11 @@
       <c r="BM7" s="173"/>
       <c r="BN7" s="173"/>
       <c r="BO7" s="173"/>
-      <c r="BP7" s="225"/>
-      <c r="BQ7" s="225"/>
-      <c r="BR7" s="225"/>
-      <c r="BS7" s="225"/>
-      <c r="BT7" s="225"/>
+      <c r="BP7" s="226"/>
+      <c r="BQ7" s="226"/>
+      <c r="BR7" s="226"/>
+      <c r="BS7" s="226"/>
+      <c r="BT7" s="226"/>
       <c r="BU7" s="173"/>
       <c r="BV7" s="173"/>
       <c r="BW7" s="173"/>
@@ -27718,11 +27718,11 @@
       <c r="BA8" s="173"/>
       <c r="BB8" s="173"/>
       <c r="BC8" s="173"/>
-      <c r="BD8" s="225"/>
-      <c r="BE8" s="225"/>
-      <c r="BF8" s="225"/>
-      <c r="BG8" s="225"/>
-      <c r="BH8" s="225"/>
+      <c r="BD8" s="226"/>
+      <c r="BE8" s="226"/>
+      <c r="BF8" s="226"/>
+      <c r="BG8" s="226"/>
+      <c r="BH8" s="226"/>
       <c r="BI8" s="173"/>
       <c r="BJ8" s="173"/>
       <c r="BK8" s="173"/>
@@ -27730,11 +27730,11 @@
       <c r="BM8" s="173"/>
       <c r="BN8" s="173"/>
       <c r="BO8" s="173"/>
-      <c r="BP8" s="225"/>
-      <c r="BQ8" s="225"/>
-      <c r="BR8" s="225"/>
-      <c r="BS8" s="225"/>
-      <c r="BT8" s="225"/>
+      <c r="BP8" s="226"/>
+      <c r="BQ8" s="226"/>
+      <c r="BR8" s="226"/>
+      <c r="BS8" s="226"/>
+      <c r="BT8" s="226"/>
       <c r="BU8" s="173"/>
       <c r="BV8" s="173"/>
       <c r="BW8" s="173"/>
@@ -27994,16 +27994,16 @@
       <c r="BF14" s="181"/>
       <c r="BG14" s="181"/>
       <c r="BH14" s="181"/>
-      <c r="BI14" s="227" t="s">
+      <c r="BI14" s="228" t="s">
         <v>138</v>
       </c>
-      <c r="BJ14" s="227"/>
-      <c r="BK14" s="227"/>
-      <c r="BL14" s="227"/>
-      <c r="BM14" s="227"/>
-      <c r="BN14" s="227"/>
-      <c r="BO14" s="227"/>
-      <c r="BP14" s="227"/>
+      <c r="BJ14" s="228"/>
+      <c r="BK14" s="228"/>
+      <c r="BL14" s="228"/>
+      <c r="BM14" s="228"/>
+      <c r="BN14" s="228"/>
+      <c r="BO14" s="228"/>
+      <c r="BP14" s="228"/>
       <c r="BQ14" s="173"/>
       <c r="BR14" s="173"/>
       <c r="BS14" s="173"/>
@@ -28081,16 +28081,16 @@
       <c r="BF15" s="181"/>
       <c r="BG15" s="181"/>
       <c r="BH15" s="181"/>
-      <c r="BI15" s="227" t="s">
+      <c r="BI15" s="228" t="s">
         <v>133</v>
       </c>
-      <c r="BJ15" s="227"/>
-      <c r="BK15" s="227"/>
-      <c r="BL15" s="227"/>
-      <c r="BM15" s="227"/>
-      <c r="BN15" s="227"/>
-      <c r="BO15" s="227"/>
-      <c r="BP15" s="227"/>
+      <c r="BJ15" s="228"/>
+      <c r="BK15" s="228"/>
+      <c r="BL15" s="228"/>
+      <c r="BM15" s="228"/>
+      <c r="BN15" s="228"/>
+      <c r="BO15" s="228"/>
+      <c r="BP15" s="228"/>
       <c r="BQ15" s="173"/>
       <c r="BR15" s="173"/>
       <c r="BS15" s="173"/>
@@ -28168,16 +28168,16 @@
       <c r="BF16" s="181"/>
       <c r="BG16" s="181"/>
       <c r="BH16" s="181"/>
-      <c r="BI16" s="227" t="s">
+      <c r="BI16" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ16" s="227"/>
-      <c r="BK16" s="227"/>
-      <c r="BL16" s="227"/>
-      <c r="BM16" s="227"/>
-      <c r="BN16" s="227"/>
-      <c r="BO16" s="227"/>
-      <c r="BP16" s="227"/>
+      <c r="BJ16" s="228"/>
+      <c r="BK16" s="228"/>
+      <c r="BL16" s="228"/>
+      <c r="BM16" s="228"/>
+      <c r="BN16" s="228"/>
+      <c r="BO16" s="228"/>
+      <c r="BP16" s="228"/>
       <c r="BQ16" s="173"/>
       <c r="BR16" s="173"/>
       <c r="BS16" s="173"/>
@@ -28255,16 +28255,16 @@
       <c r="BF17" s="181"/>
       <c r="BG17" s="181"/>
       <c r="BH17" s="181"/>
-      <c r="BI17" s="227" t="s">
+      <c r="BI17" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ17" s="227"/>
-      <c r="BK17" s="227"/>
-      <c r="BL17" s="227"/>
-      <c r="BM17" s="227"/>
-      <c r="BN17" s="227"/>
-      <c r="BO17" s="227"/>
-      <c r="BP17" s="227"/>
+      <c r="BJ17" s="228"/>
+      <c r="BK17" s="228"/>
+      <c r="BL17" s="228"/>
+      <c r="BM17" s="228"/>
+      <c r="BN17" s="228"/>
+      <c r="BO17" s="228"/>
+      <c r="BP17" s="228"/>
       <c r="BQ17" s="173"/>
       <c r="BR17" s="173"/>
       <c r="BS17" s="173"/>
@@ -28342,16 +28342,16 @@
       <c r="BF18" s="181"/>
       <c r="BG18" s="181"/>
       <c r="BH18" s="181"/>
-      <c r="BI18" s="227" t="s">
+      <c r="BI18" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ18" s="227"/>
-      <c r="BK18" s="227"/>
-      <c r="BL18" s="227"/>
-      <c r="BM18" s="227"/>
-      <c r="BN18" s="227"/>
-      <c r="BO18" s="227"/>
-      <c r="BP18" s="227"/>
+      <c r="BJ18" s="228"/>
+      <c r="BK18" s="228"/>
+      <c r="BL18" s="228"/>
+      <c r="BM18" s="228"/>
+      <c r="BN18" s="228"/>
+      <c r="BO18" s="228"/>
+      <c r="BP18" s="228"/>
       <c r="BQ18" s="173"/>
       <c r="BR18" s="173"/>
       <c r="BS18" s="173"/>
@@ -28408,37 +28408,37 @@
       <c r="AO19" s="51"/>
       <c r="AP19" s="51"/>
       <c r="AQ19" s="51"/>
-      <c r="AR19" s="201">
+      <c r="AR19" s="202">
         <v>6</v>
       </c>
-      <c r="AS19" s="202"/>
-      <c r="AT19" s="229" t="s">
+      <c r="AS19" s="203"/>
+      <c r="AT19" s="230" t="s">
         <v>173</v>
       </c>
-      <c r="AU19" s="230"/>
-      <c r="AV19" s="230"/>
-      <c r="AW19" s="230"/>
-      <c r="AX19" s="230"/>
-      <c r="AY19" s="230"/>
-      <c r="AZ19" s="230"/>
-      <c r="BA19" s="230"/>
-      <c r="BB19" s="230"/>
-      <c r="BC19" s="230"/>
-      <c r="BD19" s="230"/>
-      <c r="BE19" s="230"/>
-      <c r="BF19" s="230"/>
-      <c r="BG19" s="230"/>
-      <c r="BH19" s="231"/>
-      <c r="BI19" s="229" t="s">
+      <c r="AU19" s="231"/>
+      <c r="AV19" s="231"/>
+      <c r="AW19" s="231"/>
+      <c r="AX19" s="231"/>
+      <c r="AY19" s="231"/>
+      <c r="AZ19" s="231"/>
+      <c r="BA19" s="231"/>
+      <c r="BB19" s="231"/>
+      <c r="BC19" s="231"/>
+      <c r="BD19" s="231"/>
+      <c r="BE19" s="231"/>
+      <c r="BF19" s="231"/>
+      <c r="BG19" s="231"/>
+      <c r="BH19" s="232"/>
+      <c r="BI19" s="230" t="s">
         <v>182</v>
       </c>
-      <c r="BJ19" s="230"/>
-      <c r="BK19" s="230"/>
-      <c r="BL19" s="230"/>
-      <c r="BM19" s="230"/>
-      <c r="BN19" s="230"/>
-      <c r="BO19" s="230"/>
-      <c r="BP19" s="231"/>
+      <c r="BJ19" s="231"/>
+      <c r="BK19" s="231"/>
+      <c r="BL19" s="231"/>
+      <c r="BM19" s="231"/>
+      <c r="BN19" s="231"/>
+      <c r="BO19" s="231"/>
+      <c r="BP19" s="232"/>
       <c r="BQ19" s="185"/>
       <c r="BR19" s="186"/>
       <c r="BS19" s="186"/>
@@ -28495,31 +28495,31 @@
       <c r="AO20" s="51"/>
       <c r="AP20" s="51"/>
       <c r="AQ20" s="51"/>
-      <c r="AR20" s="205"/>
-      <c r="AS20" s="206"/>
-      <c r="AT20" s="232"/>
-      <c r="AU20" s="233"/>
-      <c r="AV20" s="233"/>
-      <c r="AW20" s="233"/>
-      <c r="AX20" s="233"/>
-      <c r="AY20" s="233"/>
-      <c r="AZ20" s="233"/>
-      <c r="BA20" s="233"/>
-      <c r="BB20" s="233"/>
-      <c r="BC20" s="233"/>
-      <c r="BD20" s="233"/>
-      <c r="BE20" s="233"/>
-      <c r="BF20" s="233"/>
-      <c r="BG20" s="233"/>
-      <c r="BH20" s="234"/>
-      <c r="BI20" s="232"/>
-      <c r="BJ20" s="233"/>
-      <c r="BK20" s="233"/>
-      <c r="BL20" s="233"/>
-      <c r="BM20" s="233"/>
-      <c r="BN20" s="233"/>
-      <c r="BO20" s="233"/>
-      <c r="BP20" s="234"/>
+      <c r="AR20" s="206"/>
+      <c r="AS20" s="207"/>
+      <c r="AT20" s="233"/>
+      <c r="AU20" s="234"/>
+      <c r="AV20" s="234"/>
+      <c r="AW20" s="234"/>
+      <c r="AX20" s="234"/>
+      <c r="AY20" s="234"/>
+      <c r="AZ20" s="234"/>
+      <c r="BA20" s="234"/>
+      <c r="BB20" s="234"/>
+      <c r="BC20" s="234"/>
+      <c r="BD20" s="234"/>
+      <c r="BE20" s="234"/>
+      <c r="BF20" s="234"/>
+      <c r="BG20" s="234"/>
+      <c r="BH20" s="235"/>
+      <c r="BI20" s="233"/>
+      <c r="BJ20" s="234"/>
+      <c r="BK20" s="234"/>
+      <c r="BL20" s="234"/>
+      <c r="BM20" s="234"/>
+      <c r="BN20" s="234"/>
+      <c r="BO20" s="234"/>
+      <c r="BP20" s="235"/>
       <c r="BQ20" s="191"/>
       <c r="BR20" s="192"/>
       <c r="BS20" s="192"/>
@@ -28576,37 +28576,37 @@
       <c r="AO21" s="51"/>
       <c r="AP21" s="51"/>
       <c r="AQ21" s="51"/>
-      <c r="AR21" s="201">
+      <c r="AR21" s="202">
         <v>7</v>
       </c>
-      <c r="AS21" s="202"/>
-      <c r="AT21" s="229" t="s">
+      <c r="AS21" s="203"/>
+      <c r="AT21" s="230" t="s">
         <v>174</v>
       </c>
-      <c r="AU21" s="230"/>
-      <c r="AV21" s="230"/>
-      <c r="AW21" s="230"/>
-      <c r="AX21" s="230"/>
-      <c r="AY21" s="230"/>
-      <c r="AZ21" s="230"/>
-      <c r="BA21" s="230"/>
-      <c r="BB21" s="230"/>
-      <c r="BC21" s="230"/>
-      <c r="BD21" s="230"/>
-      <c r="BE21" s="230"/>
-      <c r="BF21" s="230"/>
-      <c r="BG21" s="230"/>
-      <c r="BH21" s="231"/>
-      <c r="BI21" s="235" t="s">
+      <c r="AU21" s="231"/>
+      <c r="AV21" s="231"/>
+      <c r="AW21" s="231"/>
+      <c r="AX21" s="231"/>
+      <c r="AY21" s="231"/>
+      <c r="AZ21" s="231"/>
+      <c r="BA21" s="231"/>
+      <c r="BB21" s="231"/>
+      <c r="BC21" s="231"/>
+      <c r="BD21" s="231"/>
+      <c r="BE21" s="231"/>
+      <c r="BF21" s="231"/>
+      <c r="BG21" s="231"/>
+      <c r="BH21" s="232"/>
+      <c r="BI21" s="236" t="s">
         <v>183</v>
       </c>
-      <c r="BJ21" s="228"/>
-      <c r="BK21" s="228"/>
-      <c r="BL21" s="228"/>
-      <c r="BM21" s="228"/>
-      <c r="BN21" s="228"/>
-      <c r="BO21" s="228"/>
-      <c r="BP21" s="236"/>
+      <c r="BJ21" s="229"/>
+      <c r="BK21" s="229"/>
+      <c r="BL21" s="229"/>
+      <c r="BM21" s="229"/>
+      <c r="BN21" s="229"/>
+      <c r="BO21" s="229"/>
+      <c r="BP21" s="237"/>
       <c r="BQ21" s="185"/>
       <c r="BR21" s="186"/>
       <c r="BS21" s="186"/>
@@ -28663,31 +28663,31 @@
       <c r="AO22" s="51"/>
       <c r="AP22" s="51"/>
       <c r="AQ22" s="51"/>
-      <c r="AR22" s="205"/>
-      <c r="AS22" s="206"/>
-      <c r="AT22" s="232"/>
-      <c r="AU22" s="233"/>
-      <c r="AV22" s="233"/>
-      <c r="AW22" s="233"/>
-      <c r="AX22" s="233"/>
-      <c r="AY22" s="233"/>
-      <c r="AZ22" s="233"/>
-      <c r="BA22" s="233"/>
-      <c r="BB22" s="233"/>
-      <c r="BC22" s="233"/>
-      <c r="BD22" s="233"/>
-      <c r="BE22" s="233"/>
-      <c r="BF22" s="233"/>
-      <c r="BG22" s="233"/>
-      <c r="BH22" s="234"/>
-      <c r="BI22" s="237"/>
-      <c r="BJ22" s="238"/>
-      <c r="BK22" s="238"/>
-      <c r="BL22" s="238"/>
-      <c r="BM22" s="238"/>
-      <c r="BN22" s="238"/>
-      <c r="BO22" s="238"/>
-      <c r="BP22" s="239"/>
+      <c r="AR22" s="206"/>
+      <c r="AS22" s="207"/>
+      <c r="AT22" s="233"/>
+      <c r="AU22" s="234"/>
+      <c r="AV22" s="234"/>
+      <c r="AW22" s="234"/>
+      <c r="AX22" s="234"/>
+      <c r="AY22" s="234"/>
+      <c r="AZ22" s="234"/>
+      <c r="BA22" s="234"/>
+      <c r="BB22" s="234"/>
+      <c r="BC22" s="234"/>
+      <c r="BD22" s="234"/>
+      <c r="BE22" s="234"/>
+      <c r="BF22" s="234"/>
+      <c r="BG22" s="234"/>
+      <c r="BH22" s="235"/>
+      <c r="BI22" s="238"/>
+      <c r="BJ22" s="239"/>
+      <c r="BK22" s="239"/>
+      <c r="BL22" s="239"/>
+      <c r="BM22" s="239"/>
+      <c r="BN22" s="239"/>
+      <c r="BO22" s="239"/>
+      <c r="BP22" s="240"/>
       <c r="BQ22" s="191"/>
       <c r="BR22" s="192"/>
       <c r="BS22" s="192"/>
@@ -28748,33 +28748,33 @@
         <v>8</v>
       </c>
       <c r="AS23" s="180"/>
-      <c r="AT23" s="228" t="s">
+      <c r="AT23" s="229" t="s">
         <v>175</v>
       </c>
-      <c r="AU23" s="228"/>
-      <c r="AV23" s="228"/>
-      <c r="AW23" s="228"/>
-      <c r="AX23" s="228"/>
-      <c r="AY23" s="228"/>
-      <c r="AZ23" s="228"/>
-      <c r="BA23" s="228"/>
-      <c r="BB23" s="228"/>
-      <c r="BC23" s="228"/>
-      <c r="BD23" s="228"/>
-      <c r="BE23" s="228"/>
-      <c r="BF23" s="228"/>
-      <c r="BG23" s="228"/>
-      <c r="BH23" s="228"/>
-      <c r="BI23" s="227" t="s">
+      <c r="AU23" s="229"/>
+      <c r="AV23" s="229"/>
+      <c r="AW23" s="229"/>
+      <c r="AX23" s="229"/>
+      <c r="AY23" s="229"/>
+      <c r="AZ23" s="229"/>
+      <c r="BA23" s="229"/>
+      <c r="BB23" s="229"/>
+      <c r="BC23" s="229"/>
+      <c r="BD23" s="229"/>
+      <c r="BE23" s="229"/>
+      <c r="BF23" s="229"/>
+      <c r="BG23" s="229"/>
+      <c r="BH23" s="229"/>
+      <c r="BI23" s="228" t="s">
         <v>184</v>
       </c>
-      <c r="BJ23" s="227"/>
-      <c r="BK23" s="227"/>
-      <c r="BL23" s="227"/>
-      <c r="BM23" s="227"/>
-      <c r="BN23" s="227"/>
-      <c r="BO23" s="227"/>
-      <c r="BP23" s="227"/>
+      <c r="BJ23" s="228"/>
+      <c r="BK23" s="228"/>
+      <c r="BL23" s="228"/>
+      <c r="BM23" s="228"/>
+      <c r="BN23" s="228"/>
+      <c r="BO23" s="228"/>
+      <c r="BP23" s="228"/>
       <c r="BQ23" s="173"/>
       <c r="BR23" s="173"/>
       <c r="BS23" s="173"/>
@@ -28835,33 +28835,33 @@
         <v>9</v>
       </c>
       <c r="AS24" s="180"/>
-      <c r="AT24" s="228" t="s">
+      <c r="AT24" s="229" t="s">
         <v>176</v>
       </c>
-      <c r="AU24" s="228"/>
-      <c r="AV24" s="228"/>
-      <c r="AW24" s="228"/>
-      <c r="AX24" s="228"/>
-      <c r="AY24" s="228"/>
-      <c r="AZ24" s="228"/>
-      <c r="BA24" s="228"/>
-      <c r="BB24" s="228"/>
-      <c r="BC24" s="228"/>
-      <c r="BD24" s="228"/>
-      <c r="BE24" s="228"/>
-      <c r="BF24" s="228"/>
-      <c r="BG24" s="228"/>
-      <c r="BH24" s="228"/>
-      <c r="BI24" s="227" t="s">
+      <c r="AU24" s="229"/>
+      <c r="AV24" s="229"/>
+      <c r="AW24" s="229"/>
+      <c r="AX24" s="229"/>
+      <c r="AY24" s="229"/>
+      <c r="AZ24" s="229"/>
+      <c r="BA24" s="229"/>
+      <c r="BB24" s="229"/>
+      <c r="BC24" s="229"/>
+      <c r="BD24" s="229"/>
+      <c r="BE24" s="229"/>
+      <c r="BF24" s="229"/>
+      <c r="BG24" s="229"/>
+      <c r="BH24" s="229"/>
+      <c r="BI24" s="228" t="s">
         <v>185</v>
       </c>
-      <c r="BJ24" s="227"/>
-      <c r="BK24" s="227"/>
-      <c r="BL24" s="227"/>
-      <c r="BM24" s="227"/>
-      <c r="BN24" s="227"/>
-      <c r="BO24" s="227"/>
-      <c r="BP24" s="227"/>
+      <c r="BJ24" s="228"/>
+      <c r="BK24" s="228"/>
+      <c r="BL24" s="228"/>
+      <c r="BM24" s="228"/>
+      <c r="BN24" s="228"/>
+      <c r="BO24" s="228"/>
+      <c r="BP24" s="228"/>
       <c r="BQ24" s="173"/>
       <c r="BR24" s="173"/>
       <c r="BS24" s="173"/>
@@ -28922,33 +28922,33 @@
         <v>10</v>
       </c>
       <c r="AS25" s="180"/>
-      <c r="AT25" s="230" t="s">
+      <c r="AT25" s="231" t="s">
         <v>236</v>
       </c>
-      <c r="AU25" s="230"/>
-      <c r="AV25" s="230"/>
-      <c r="AW25" s="230"/>
-      <c r="AX25" s="230"/>
-      <c r="AY25" s="230"/>
-      <c r="AZ25" s="230"/>
-      <c r="BA25" s="230"/>
-      <c r="BB25" s="230"/>
-      <c r="BC25" s="230"/>
-      <c r="BD25" s="230"/>
-      <c r="BE25" s="230"/>
-      <c r="BF25" s="230"/>
-      <c r="BG25" s="230"/>
-      <c r="BH25" s="230"/>
-      <c r="BI25" s="235" t="s">
+      <c r="AU25" s="231"/>
+      <c r="AV25" s="231"/>
+      <c r="AW25" s="231"/>
+      <c r="AX25" s="231"/>
+      <c r="AY25" s="231"/>
+      <c r="AZ25" s="231"/>
+      <c r="BA25" s="231"/>
+      <c r="BB25" s="231"/>
+      <c r="BC25" s="231"/>
+      <c r="BD25" s="231"/>
+      <c r="BE25" s="231"/>
+      <c r="BF25" s="231"/>
+      <c r="BG25" s="231"/>
+      <c r="BH25" s="231"/>
+      <c r="BI25" s="236" t="s">
         <v>133</v>
       </c>
-      <c r="BJ25" s="228"/>
-      <c r="BK25" s="228"/>
-      <c r="BL25" s="228"/>
-      <c r="BM25" s="228"/>
-      <c r="BN25" s="228"/>
-      <c r="BO25" s="228"/>
-      <c r="BP25" s="236"/>
+      <c r="BJ25" s="229"/>
+      <c r="BK25" s="229"/>
+      <c r="BL25" s="229"/>
+      <c r="BM25" s="229"/>
+      <c r="BN25" s="229"/>
+      <c r="BO25" s="229"/>
+      <c r="BP25" s="237"/>
       <c r="BQ25" s="185"/>
       <c r="BR25" s="186"/>
       <c r="BS25" s="186"/>
@@ -29007,29 +29007,29 @@
       <c r="AQ26" s="51"/>
       <c r="AR26" s="180"/>
       <c r="AS26" s="180"/>
-      <c r="AT26" s="233"/>
-      <c r="AU26" s="233"/>
-      <c r="AV26" s="233"/>
-      <c r="AW26" s="233"/>
-      <c r="AX26" s="233"/>
-      <c r="AY26" s="233"/>
-      <c r="AZ26" s="233"/>
-      <c r="BA26" s="233"/>
-      <c r="BB26" s="233"/>
-      <c r="BC26" s="233"/>
-      <c r="BD26" s="233"/>
-      <c r="BE26" s="233"/>
-      <c r="BF26" s="233"/>
-      <c r="BG26" s="233"/>
-      <c r="BH26" s="233"/>
-      <c r="BI26" s="237"/>
-      <c r="BJ26" s="238"/>
-      <c r="BK26" s="238"/>
-      <c r="BL26" s="238"/>
-      <c r="BM26" s="238"/>
-      <c r="BN26" s="238"/>
-      <c r="BO26" s="238"/>
-      <c r="BP26" s="239"/>
+      <c r="AT26" s="234"/>
+      <c r="AU26" s="234"/>
+      <c r="AV26" s="234"/>
+      <c r="AW26" s="234"/>
+      <c r="AX26" s="234"/>
+      <c r="AY26" s="234"/>
+      <c r="AZ26" s="234"/>
+      <c r="BA26" s="234"/>
+      <c r="BB26" s="234"/>
+      <c r="BC26" s="234"/>
+      <c r="BD26" s="234"/>
+      <c r="BE26" s="234"/>
+      <c r="BF26" s="234"/>
+      <c r="BG26" s="234"/>
+      <c r="BH26" s="234"/>
+      <c r="BI26" s="238"/>
+      <c r="BJ26" s="239"/>
+      <c r="BK26" s="239"/>
+      <c r="BL26" s="239"/>
+      <c r="BM26" s="239"/>
+      <c r="BN26" s="239"/>
+      <c r="BO26" s="239"/>
+      <c r="BP26" s="240"/>
       <c r="BQ26" s="191"/>
       <c r="BR26" s="192"/>
       <c r="BS26" s="192"/>
@@ -29090,33 +29090,33 @@
         <v>11</v>
       </c>
       <c r="AS27" s="180"/>
-      <c r="AT27" s="228" t="s">
+      <c r="AT27" s="229" t="s">
         <v>177</v>
       </c>
-      <c r="AU27" s="228"/>
-      <c r="AV27" s="228"/>
-      <c r="AW27" s="228"/>
-      <c r="AX27" s="228"/>
-      <c r="AY27" s="228"/>
-      <c r="AZ27" s="228"/>
-      <c r="BA27" s="228"/>
-      <c r="BB27" s="228"/>
-      <c r="BC27" s="228"/>
-      <c r="BD27" s="228"/>
-      <c r="BE27" s="228"/>
-      <c r="BF27" s="228"/>
-      <c r="BG27" s="228"/>
-      <c r="BH27" s="228"/>
-      <c r="BI27" s="227" t="s">
+      <c r="AU27" s="229"/>
+      <c r="AV27" s="229"/>
+      <c r="AW27" s="229"/>
+      <c r="AX27" s="229"/>
+      <c r="AY27" s="229"/>
+      <c r="AZ27" s="229"/>
+      <c r="BA27" s="229"/>
+      <c r="BB27" s="229"/>
+      <c r="BC27" s="229"/>
+      <c r="BD27" s="229"/>
+      <c r="BE27" s="229"/>
+      <c r="BF27" s="229"/>
+      <c r="BG27" s="229"/>
+      <c r="BH27" s="229"/>
+      <c r="BI27" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ27" s="227"/>
-      <c r="BK27" s="227"/>
-      <c r="BL27" s="227"/>
-      <c r="BM27" s="227"/>
-      <c r="BN27" s="227"/>
-      <c r="BO27" s="227"/>
-      <c r="BP27" s="227"/>
+      <c r="BJ27" s="228"/>
+      <c r="BK27" s="228"/>
+      <c r="BL27" s="228"/>
+      <c r="BM27" s="228"/>
+      <c r="BN27" s="228"/>
+      <c r="BO27" s="228"/>
+      <c r="BP27" s="228"/>
       <c r="BQ27" s="173"/>
       <c r="BR27" s="173"/>
       <c r="BS27" s="173"/>
@@ -29177,33 +29177,33 @@
         <v>12</v>
       </c>
       <c r="AS28" s="180"/>
-      <c r="AT28" s="228" t="s">
+      <c r="AT28" s="229" t="s">
         <v>178</v>
       </c>
-      <c r="AU28" s="228"/>
-      <c r="AV28" s="228"/>
-      <c r="AW28" s="228"/>
-      <c r="AX28" s="228"/>
-      <c r="AY28" s="228"/>
-      <c r="AZ28" s="228"/>
-      <c r="BA28" s="228"/>
-      <c r="BB28" s="228"/>
-      <c r="BC28" s="228"/>
-      <c r="BD28" s="228"/>
-      <c r="BE28" s="228"/>
-      <c r="BF28" s="228"/>
-      <c r="BG28" s="228"/>
-      <c r="BH28" s="228"/>
-      <c r="BI28" s="227" t="s">
+      <c r="AU28" s="229"/>
+      <c r="AV28" s="229"/>
+      <c r="AW28" s="229"/>
+      <c r="AX28" s="229"/>
+      <c r="AY28" s="229"/>
+      <c r="AZ28" s="229"/>
+      <c r="BA28" s="229"/>
+      <c r="BB28" s="229"/>
+      <c r="BC28" s="229"/>
+      <c r="BD28" s="229"/>
+      <c r="BE28" s="229"/>
+      <c r="BF28" s="229"/>
+      <c r="BG28" s="229"/>
+      <c r="BH28" s="229"/>
+      <c r="BI28" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ28" s="227"/>
-      <c r="BK28" s="227"/>
-      <c r="BL28" s="227"/>
-      <c r="BM28" s="227"/>
-      <c r="BN28" s="227"/>
-      <c r="BO28" s="227"/>
-      <c r="BP28" s="227"/>
+      <c r="BJ28" s="228"/>
+      <c r="BK28" s="228"/>
+      <c r="BL28" s="228"/>
+      <c r="BM28" s="228"/>
+      <c r="BN28" s="228"/>
+      <c r="BO28" s="228"/>
+      <c r="BP28" s="228"/>
       <c r="BQ28" s="173"/>
       <c r="BR28" s="173"/>
       <c r="BS28" s="173"/>
@@ -29260,37 +29260,37 @@
       <c r="AO29" s="51"/>
       <c r="AP29" s="51"/>
       <c r="AQ29" s="51"/>
-      <c r="AR29" s="201">
+      <c r="AR29" s="202">
         <v>13</v>
       </c>
-      <c r="AS29" s="202"/>
-      <c r="AT29" s="235" t="s">
+      <c r="AS29" s="203"/>
+      <c r="AT29" s="236" t="s">
         <v>179</v>
       </c>
-      <c r="AU29" s="228"/>
-      <c r="AV29" s="228"/>
-      <c r="AW29" s="228"/>
-      <c r="AX29" s="228"/>
-      <c r="AY29" s="228"/>
-      <c r="AZ29" s="228"/>
-      <c r="BA29" s="228"/>
-      <c r="BB29" s="228"/>
-      <c r="BC29" s="228"/>
-      <c r="BD29" s="228"/>
-      <c r="BE29" s="228"/>
-      <c r="BF29" s="228"/>
-      <c r="BG29" s="228"/>
-      <c r="BH29" s="236"/>
-      <c r="BI29" s="229" t="s">
+      <c r="AU29" s="229"/>
+      <c r="AV29" s="229"/>
+      <c r="AW29" s="229"/>
+      <c r="AX29" s="229"/>
+      <c r="AY29" s="229"/>
+      <c r="AZ29" s="229"/>
+      <c r="BA29" s="229"/>
+      <c r="BB29" s="229"/>
+      <c r="BC29" s="229"/>
+      <c r="BD29" s="229"/>
+      <c r="BE29" s="229"/>
+      <c r="BF29" s="229"/>
+      <c r="BG29" s="229"/>
+      <c r="BH29" s="237"/>
+      <c r="BI29" s="230" t="s">
         <v>186</v>
       </c>
-      <c r="BJ29" s="230"/>
-      <c r="BK29" s="230"/>
-      <c r="BL29" s="230"/>
-      <c r="BM29" s="230"/>
-      <c r="BN29" s="230"/>
-      <c r="BO29" s="230"/>
-      <c r="BP29" s="231"/>
+      <c r="BJ29" s="231"/>
+      <c r="BK29" s="231"/>
+      <c r="BL29" s="231"/>
+      <c r="BM29" s="231"/>
+      <c r="BN29" s="231"/>
+      <c r="BO29" s="231"/>
+      <c r="BP29" s="232"/>
       <c r="BQ29" s="185"/>
       <c r="BR29" s="186"/>
       <c r="BS29" s="186"/>
@@ -29347,31 +29347,31 @@
       <c r="AO30" s="51"/>
       <c r="AP30" s="51"/>
       <c r="AQ30" s="51"/>
-      <c r="AR30" s="205"/>
-      <c r="AS30" s="206"/>
-      <c r="AT30" s="237"/>
-      <c r="AU30" s="238"/>
-      <c r="AV30" s="238"/>
-      <c r="AW30" s="238"/>
-      <c r="AX30" s="238"/>
-      <c r="AY30" s="238"/>
-      <c r="AZ30" s="238"/>
-      <c r="BA30" s="238"/>
-      <c r="BB30" s="238"/>
-      <c r="BC30" s="238"/>
-      <c r="BD30" s="238"/>
-      <c r="BE30" s="238"/>
-      <c r="BF30" s="238"/>
-      <c r="BG30" s="238"/>
-      <c r="BH30" s="239"/>
-      <c r="BI30" s="232"/>
-      <c r="BJ30" s="233"/>
-      <c r="BK30" s="233"/>
-      <c r="BL30" s="233"/>
-      <c r="BM30" s="233"/>
-      <c r="BN30" s="233"/>
-      <c r="BO30" s="233"/>
-      <c r="BP30" s="234"/>
+      <c r="AR30" s="206"/>
+      <c r="AS30" s="207"/>
+      <c r="AT30" s="238"/>
+      <c r="AU30" s="239"/>
+      <c r="AV30" s="239"/>
+      <c r="AW30" s="239"/>
+      <c r="AX30" s="239"/>
+      <c r="AY30" s="239"/>
+      <c r="AZ30" s="239"/>
+      <c r="BA30" s="239"/>
+      <c r="BB30" s="239"/>
+      <c r="BC30" s="239"/>
+      <c r="BD30" s="239"/>
+      <c r="BE30" s="239"/>
+      <c r="BF30" s="239"/>
+      <c r="BG30" s="239"/>
+      <c r="BH30" s="240"/>
+      <c r="BI30" s="233"/>
+      <c r="BJ30" s="234"/>
+      <c r="BK30" s="234"/>
+      <c r="BL30" s="234"/>
+      <c r="BM30" s="234"/>
+      <c r="BN30" s="234"/>
+      <c r="BO30" s="234"/>
+      <c r="BP30" s="235"/>
       <c r="BQ30" s="191"/>
       <c r="BR30" s="192"/>
       <c r="BS30" s="192"/>
@@ -29432,33 +29432,33 @@
         <v>14</v>
       </c>
       <c r="AS31" s="180"/>
-      <c r="AT31" s="228" t="s">
+      <c r="AT31" s="229" t="s">
         <v>180</v>
       </c>
-      <c r="AU31" s="228"/>
-      <c r="AV31" s="228"/>
-      <c r="AW31" s="228"/>
-      <c r="AX31" s="228"/>
-      <c r="AY31" s="228"/>
-      <c r="AZ31" s="228"/>
-      <c r="BA31" s="228"/>
-      <c r="BB31" s="228"/>
-      <c r="BC31" s="228"/>
-      <c r="BD31" s="228"/>
-      <c r="BE31" s="228"/>
-      <c r="BF31" s="228"/>
-      <c r="BG31" s="228"/>
-      <c r="BH31" s="228"/>
-      <c r="BI31" s="227" t="s">
+      <c r="AU31" s="229"/>
+      <c r="AV31" s="229"/>
+      <c r="AW31" s="229"/>
+      <c r="AX31" s="229"/>
+      <c r="AY31" s="229"/>
+      <c r="AZ31" s="229"/>
+      <c r="BA31" s="229"/>
+      <c r="BB31" s="229"/>
+      <c r="BC31" s="229"/>
+      <c r="BD31" s="229"/>
+      <c r="BE31" s="229"/>
+      <c r="BF31" s="229"/>
+      <c r="BG31" s="229"/>
+      <c r="BH31" s="229"/>
+      <c r="BI31" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ31" s="227"/>
-      <c r="BK31" s="227"/>
-      <c r="BL31" s="227"/>
-      <c r="BM31" s="227"/>
-      <c r="BN31" s="227"/>
-      <c r="BO31" s="227"/>
-      <c r="BP31" s="227"/>
+      <c r="BJ31" s="228"/>
+      <c r="BK31" s="228"/>
+      <c r="BL31" s="228"/>
+      <c r="BM31" s="228"/>
+      <c r="BN31" s="228"/>
+      <c r="BO31" s="228"/>
+      <c r="BP31" s="228"/>
       <c r="BQ31" s="173"/>
       <c r="BR31" s="173"/>
       <c r="BS31" s="173"/>
@@ -29519,33 +29519,33 @@
         <v>15</v>
       </c>
       <c r="AS32" s="180"/>
-      <c r="AT32" s="228" t="s">
+      <c r="AT32" s="229" t="s">
         <v>181</v>
       </c>
-      <c r="AU32" s="228"/>
-      <c r="AV32" s="228"/>
-      <c r="AW32" s="228"/>
-      <c r="AX32" s="228"/>
-      <c r="AY32" s="228"/>
-      <c r="AZ32" s="228"/>
-      <c r="BA32" s="228"/>
-      <c r="BB32" s="228"/>
-      <c r="BC32" s="228"/>
-      <c r="BD32" s="228"/>
-      <c r="BE32" s="228"/>
-      <c r="BF32" s="228"/>
-      <c r="BG32" s="228"/>
-      <c r="BH32" s="228"/>
-      <c r="BI32" s="227" t="s">
+      <c r="AU32" s="229"/>
+      <c r="AV32" s="229"/>
+      <c r="AW32" s="229"/>
+      <c r="AX32" s="229"/>
+      <c r="AY32" s="229"/>
+      <c r="AZ32" s="229"/>
+      <c r="BA32" s="229"/>
+      <c r="BB32" s="229"/>
+      <c r="BC32" s="229"/>
+      <c r="BD32" s="229"/>
+      <c r="BE32" s="229"/>
+      <c r="BF32" s="229"/>
+      <c r="BG32" s="229"/>
+      <c r="BH32" s="229"/>
+      <c r="BI32" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="BJ32" s="227"/>
-      <c r="BK32" s="227"/>
-      <c r="BL32" s="227"/>
-      <c r="BM32" s="227"/>
-      <c r="BN32" s="227"/>
-      <c r="BO32" s="227"/>
-      <c r="BP32" s="227"/>
+      <c r="BJ32" s="228"/>
+      <c r="BK32" s="228"/>
+      <c r="BL32" s="228"/>
+      <c r="BM32" s="228"/>
+      <c r="BN32" s="228"/>
+      <c r="BO32" s="228"/>
+      <c r="BP32" s="228"/>
       <c r="BQ32" s="173"/>
       <c r="BR32" s="173"/>
       <c r="BS32" s="173"/>
@@ -29606,33 +29606,33 @@
         <v>16</v>
       </c>
       <c r="AS33" s="180"/>
-      <c r="AT33" s="228" t="s">
+      <c r="AT33" s="229" t="s">
         <v>140</v>
       </c>
-      <c r="AU33" s="228"/>
-      <c r="AV33" s="228"/>
-      <c r="AW33" s="228"/>
-      <c r="AX33" s="228"/>
-      <c r="AY33" s="228"/>
-      <c r="AZ33" s="228"/>
-      <c r="BA33" s="228"/>
-      <c r="BB33" s="228"/>
-      <c r="BC33" s="228"/>
-      <c r="BD33" s="228"/>
-      <c r="BE33" s="228"/>
-      <c r="BF33" s="228"/>
-      <c r="BG33" s="228"/>
-      <c r="BH33" s="228"/>
-      <c r="BI33" s="227" t="s">
+      <c r="AU33" s="229"/>
+      <c r="AV33" s="229"/>
+      <c r="AW33" s="229"/>
+      <c r="AX33" s="229"/>
+      <c r="AY33" s="229"/>
+      <c r="AZ33" s="229"/>
+      <c r="BA33" s="229"/>
+      <c r="BB33" s="229"/>
+      <c r="BC33" s="229"/>
+      <c r="BD33" s="229"/>
+      <c r="BE33" s="229"/>
+      <c r="BF33" s="229"/>
+      <c r="BG33" s="229"/>
+      <c r="BH33" s="229"/>
+      <c r="BI33" s="228" t="s">
         <v>134</v>
       </c>
-      <c r="BJ33" s="227"/>
-      <c r="BK33" s="227"/>
-      <c r="BL33" s="227"/>
-      <c r="BM33" s="227"/>
-      <c r="BN33" s="227"/>
-      <c r="BO33" s="227"/>
-      <c r="BP33" s="227"/>
+      <c r="BJ33" s="228"/>
+      <c r="BK33" s="228"/>
+      <c r="BL33" s="228"/>
+      <c r="BM33" s="228"/>
+      <c r="BN33" s="228"/>
+      <c r="BO33" s="228"/>
+      <c r="BP33" s="228"/>
       <c r="BQ33" s="173"/>
       <c r="BR33" s="173"/>
       <c r="BS33" s="173"/>
@@ -29693,21 +29693,21 @@
         <v>17</v>
       </c>
       <c r="AS34" s="180"/>
-      <c r="AT34" s="227"/>
-      <c r="AU34" s="227"/>
-      <c r="AV34" s="227"/>
-      <c r="AW34" s="227"/>
-      <c r="AX34" s="227"/>
-      <c r="AY34" s="227"/>
-      <c r="AZ34" s="227"/>
-      <c r="BA34" s="227"/>
-      <c r="BB34" s="227"/>
-      <c r="BC34" s="227"/>
-      <c r="BD34" s="227"/>
-      <c r="BE34" s="227"/>
-      <c r="BF34" s="227"/>
-      <c r="BG34" s="227"/>
-      <c r="BH34" s="227"/>
+      <c r="AT34" s="228"/>
+      <c r="AU34" s="228"/>
+      <c r="AV34" s="228"/>
+      <c r="AW34" s="228"/>
+      <c r="AX34" s="228"/>
+      <c r="AY34" s="228"/>
+      <c r="AZ34" s="228"/>
+      <c r="BA34" s="228"/>
+      <c r="BB34" s="228"/>
+      <c r="BC34" s="228"/>
+      <c r="BD34" s="228"/>
+      <c r="BE34" s="228"/>
+      <c r="BF34" s="228"/>
+      <c r="BG34" s="228"/>
+      <c r="BH34" s="228"/>
       <c r="BI34" s="184"/>
       <c r="BJ34" s="184"/>
       <c r="BK34" s="184"/>
@@ -29774,21 +29774,21 @@
       <c r="AQ35" s="51"/>
       <c r="AR35" s="180"/>
       <c r="AS35" s="180"/>
-      <c r="AT35" s="227"/>
-      <c r="AU35" s="227"/>
-      <c r="AV35" s="227"/>
-      <c r="AW35" s="227"/>
-      <c r="AX35" s="227"/>
-      <c r="AY35" s="227"/>
-      <c r="AZ35" s="227"/>
-      <c r="BA35" s="227"/>
-      <c r="BB35" s="227"/>
-      <c r="BC35" s="227"/>
-      <c r="BD35" s="227"/>
-      <c r="BE35" s="227"/>
-      <c r="BF35" s="227"/>
-      <c r="BG35" s="227"/>
-      <c r="BH35" s="227"/>
+      <c r="AT35" s="228"/>
+      <c r="AU35" s="228"/>
+      <c r="AV35" s="228"/>
+      <c r="AW35" s="228"/>
+      <c r="AX35" s="228"/>
+      <c r="AY35" s="228"/>
+      <c r="AZ35" s="228"/>
+      <c r="BA35" s="228"/>
+      <c r="BB35" s="228"/>
+      <c r="BC35" s="228"/>
+      <c r="BD35" s="228"/>
+      <c r="BE35" s="228"/>
+      <c r="BF35" s="228"/>
+      <c r="BG35" s="228"/>
+      <c r="BH35" s="228"/>
       <c r="BI35" s="184"/>
       <c r="BJ35" s="184"/>
       <c r="BK35" s="184"/>
@@ -30079,10 +30079,10 @@
       </c>
       <c r="BH44" s="171"/>
       <c r="BI44" s="171"/>
-      <c r="BJ44" s="240"/>
-      <c r="BK44" s="240"/>
-      <c r="BL44" s="240"/>
-      <c r="BM44" s="240"/>
+      <c r="BJ44" s="201"/>
+      <c r="BK44" s="201"/>
+      <c r="BL44" s="201"/>
+      <c r="BM44" s="201"/>
       <c r="BN44" s="35" t="s">
         <v>159</v>
       </c>
@@ -34220,9 +34220,9 @@
       <c r="AR2" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="BS2" s="226"/>
-      <c r="BT2" s="226"/>
-      <c r="BU2" s="226"/>
+      <c r="BS2" s="227"/>
+      <c r="BT2" s="227"/>
+      <c r="BU2" s="227"/>
       <c r="BV2" s="13" t="s">
         <v>344</v>
       </c>
@@ -34336,9 +34336,9 @@
       <c r="BD5" s="171"/>
       <c r="BE5" s="171"/>
       <c r="BF5" s="171"/>
-      <c r="BG5" s="240"/>
-      <c r="BH5" s="240"/>
-      <c r="BI5" s="240"/>
+      <c r="BG5" s="201"/>
+      <c r="BH5" s="201"/>
+      <c r="BI5" s="201"/>
       <c r="BJ5" s="34" t="s">
         <v>100</v>
       </c>
@@ -36397,32 +36397,32 @@
       <c r="BG40" s="173"/>
       <c r="BH40" s="173"/>
       <c r="BI40" s="173"/>
-      <c r="BJ40" s="262" t="s">
+      <c r="BJ40" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="BK40" s="263"/>
-      <c r="BL40" s="263"/>
-      <c r="BM40" s="350"/>
-      <c r="BN40" s="350"/>
-      <c r="BO40" s="260" t="s">
+      <c r="BK40" s="264"/>
+      <c r="BL40" s="264"/>
+      <c r="BM40" s="260"/>
+      <c r="BN40" s="260"/>
+      <c r="BO40" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="BP40" s="260"/>
-      <c r="BQ40" s="260"/>
-      <c r="BR40" s="261"/>
-      <c r="BS40" s="262" t="s">
+      <c r="BP40" s="261"/>
+      <c r="BQ40" s="261"/>
+      <c r="BR40" s="262"/>
+      <c r="BS40" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="BT40" s="263"/>
-      <c r="BU40" s="263"/>
-      <c r="BV40" s="350"/>
-      <c r="BW40" s="350"/>
-      <c r="BX40" s="260" t="s">
+      <c r="BT40" s="264"/>
+      <c r="BU40" s="264"/>
+      <c r="BV40" s="260"/>
+      <c r="BW40" s="260"/>
+      <c r="BX40" s="261" t="s">
         <v>202</v>
       </c>
-      <c r="BY40" s="260"/>
-      <c r="BZ40" s="260"/>
-      <c r="CA40" s="261"/>
+      <c r="BY40" s="261"/>
+      <c r="BZ40" s="261"/>
+      <c r="CA40" s="262"/>
     </row>
     <row r="41" spans="1:79" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
